--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>126864915</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126859342</v>
       </c>
       <c r="B22" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson, Vilhelm Kroon, Cajsa Björkén</t>
+          <t>Cajsa Björkén, Carl Jansson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>126864915</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126859342</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>126864915</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126859342</v>
       </c>
       <c r="B22" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3103,7 +3103,7 @@
         <v>126859342</v>
       </c>
       <c r="B22" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3209,6 +3209,6284 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128458385</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>679315</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7118058</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128458658</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>679386</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7118036</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128458657</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>679407</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7117906</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128458648</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>679482</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7118053</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128458381</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>679414</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7117929</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128458673</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>679328</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7117932</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128458365</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>679464</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7117976</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128458356</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>679480</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7117930</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128458344</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>679487</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7118042</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128458670</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>679402</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7117958</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128458399</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>679418</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7117932</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128458679</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>679434</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7118112</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128458372</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>679409</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7117952</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128458644</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91369</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>679456</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7118095</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128458386</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>679411</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7117970</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128458369</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>679437</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7117961</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128458659</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>679419</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7118102</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128458640</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>679458</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7118097</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128458364</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>679421</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7117929</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128458677</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>679355</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7118031</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128458660</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>679372</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7117955</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128458340</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>679488</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7118028</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128458384</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>679443</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7117919</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128458661</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>679395</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7117956</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128458371</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>679394</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7117935</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128458342</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>679446</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7117918</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128458653</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79056</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>679313</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7117931</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128458662</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>679403</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7117960</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128458373</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>679404</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7117977</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128458374</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>679493</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7118012</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128458388</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>679456</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7118056</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128458692</v>
+      </c>
+      <c r="B54" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>510</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>679349</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7117913</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128458643</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>679460</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7118089</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128458368</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>679446</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7117937</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128458351</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>679464</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7117976</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128458358</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>679474</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7117950</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128458350</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>679446</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7117860</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128458678</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>679369</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7118112</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128458378</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>679383</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7117814</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128458387</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>679461</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7117988</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128458367</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>679446</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7117860</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128458680</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>679472</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7118058</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128458366</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>679455</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7117858</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128458663</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>679446</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7118101</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128458353</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>679512</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7118001</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128458375</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80171</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>679437</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7117961</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128458674</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>679408</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7117925</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128458382</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>679440</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7117885</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128458672</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>679298</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7118058</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128458370</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>679433</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7117926</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128458681</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>679506</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7118062</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128458664</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>679459</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7118087</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128458671</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>679436</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7118086</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128458389</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>679512</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7118001</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128458642</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>679445</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7118102</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128458675</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>679390</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7118002</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128458349</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>679455</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7117858</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128458641</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>679393</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7118025</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128458638</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79064</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>185</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>679347</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7117856</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128458377</v>
+      </c>
+      <c r="B82" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>679279</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7118000</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128458645</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>679307</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7117932</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128472161</v>
+      </c>
+      <c r="B84" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>679389</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7117937</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128472175</v>
+      </c>
+      <c r="B85" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>510</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>679407</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7117843</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128472160</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>679384</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7118115</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458381</v>
+        <v>128458356</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679414</v>
+        <v>679480</v>
       </c>
       <c r="R27" t="n">
-        <v>7117929</v>
+        <v>7117930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,7 +3698,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3717,7 +3716,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458673</v>
+        <v>128458381</v>
       </c>
       <c r="B28" t="n">
         <v>79032</v>
@@ -3752,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679328</v>
+        <v>679414</v>
       </c>
       <c r="R28" t="n">
-        <v>7117932</v>
+        <v>7117929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,12 +3789,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3814,10 +3819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458365</v>
+        <v>128458673</v>
       </c>
       <c r="B29" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3825,21 +3830,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,10 +3854,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679464</v>
+        <v>679328</v>
       </c>
       <c r="R29" t="n">
-        <v>7117976</v>
+        <v>7117932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3893,7 +3898,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3912,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458356</v>
+        <v>128458365</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,21 +3927,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3947,10 +3951,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679480</v>
+        <v>679464</v>
       </c>
       <c r="R30" t="n">
-        <v>7117930</v>
+        <v>7117976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,17 +3989,13 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458679</v>
+        <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>91371</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679434</v>
+        <v>679456</v>
       </c>
       <c r="R34" t="n">
-        <v>7118112</v>
+        <v>7118095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458372</v>
+        <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679409</v>
+        <v>679434</v>
       </c>
       <c r="R35" t="n">
-        <v>7117952</v>
+        <v>7118112</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,32 +4499,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458644</v>
+        <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>91369</v>
+        <v>80135</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679456</v>
+        <v>679409</v>
       </c>
       <c r="R36" t="n">
-        <v>7118095</v>
+        <v>7117952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458342</v>
+        <v>128458653</v>
       </c>
       <c r="B48" t="n">
-        <v>56864</v>
+        <v>79056</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679446</v>
+        <v>679313</v>
       </c>
       <c r="R48" t="n">
-        <v>7117918</v>
+        <v>7117931</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,32 +5767,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458653</v>
+        <v>128458662</v>
       </c>
       <c r="B49" t="n">
-        <v>79056</v>
+        <v>80135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679313</v>
+        <v>679403</v>
       </c>
       <c r="R49" t="n">
-        <v>7117931</v>
+        <v>7117960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458662</v>
+        <v>128458373</v>
       </c>
       <c r="B50" t="n">
         <v>80135</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679403</v>
+        <v>679404</v>
       </c>
       <c r="R50" t="n">
-        <v>7117960</v>
+        <v>7117977</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458373</v>
+        <v>128458374</v>
       </c>
       <c r="B51" t="n">
         <v>80135</v>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679404</v>
+        <v>679493</v>
       </c>
       <c r="R51" t="n">
-        <v>7117977</v>
+        <v>7118012</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458374</v>
+        <v>128458388</v>
       </c>
       <c r="B52" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679493</v>
+        <v>679456</v>
       </c>
       <c r="R52" t="n">
-        <v>7118012</v>
+        <v>7118056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458388</v>
+        <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>56864</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679456</v>
+        <v>679446</v>
       </c>
       <c r="R53" t="n">
-        <v>7118056</v>
+        <v>7117918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B61" t="n">
-        <v>58043</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R61" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7033,32 +7033,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>58043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R62" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,10 +7246,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458680</v>
+        <v>128458353</v>
       </c>
       <c r="B64" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7257,21 +7257,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679472</v>
+        <v>679512</v>
       </c>
       <c r="R64" t="n">
-        <v>7118058</v>
+        <v>7118001</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7317,6 +7317,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7343,10 +7348,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458366</v>
+        <v>128458680</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7354,21 +7359,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7378,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679455</v>
+        <v>679472</v>
       </c>
       <c r="R65" t="n">
-        <v>7117858</v>
+        <v>7118058</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,7 +7445,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458663</v>
+        <v>128458366</v>
       </c>
       <c r="B66" t="n">
         <v>80135</v>
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679446</v>
+        <v>679455</v>
       </c>
       <c r="R66" t="n">
-        <v>7118101</v>
+        <v>7117858</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7537,10 +7542,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458353</v>
+        <v>128458663</v>
       </c>
       <c r="B67" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7548,21 +7553,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7572,10 +7577,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679512</v>
+        <v>679446</v>
       </c>
       <c r="R67" t="n">
-        <v>7118001</v>
+        <v>7118101</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7608,11 +7613,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458389</v>
+        <v>128458642</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>80164</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679512</v>
+        <v>679445</v>
       </c>
       <c r="R76" t="n">
-        <v>7118001</v>
+        <v>7118102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458642</v>
+        <v>128458389</v>
       </c>
       <c r="B77" t="n">
-        <v>80164</v>
+        <v>79032</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679445</v>
+        <v>679512</v>
       </c>
       <c r="R77" t="n">
-        <v>7118102</v>
+        <v>7118001</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8906,10 +8906,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>79064</v>
+        <v>57670</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8917,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R81" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,7 +8985,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,32 +9003,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B82" t="n">
-        <v>58043</v>
+        <v>79064</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9039,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R82" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9083,6 +9082,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9101,27 +9101,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B83" t="n">
-        <v>57670</v>
+        <v>58043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R83" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458653</v>
+        <v>128458342</v>
       </c>
       <c r="B48" t="n">
-        <v>79056</v>
+        <v>56864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679313</v>
+        <v>679446</v>
       </c>
       <c r="R48" t="n">
-        <v>7117931</v>
+        <v>7117918</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458662</v>
+        <v>128458692</v>
       </c>
       <c r="B49" t="n">
-        <v>80135</v>
+        <v>88761</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679403</v>
+        <v>679349</v>
       </c>
       <c r="R49" t="n">
-        <v>7117960</v>
+        <v>7117913</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458373</v>
+        <v>128458662</v>
       </c>
       <c r="B50" t="n">
         <v>80135</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679404</v>
+        <v>679403</v>
       </c>
       <c r="R50" t="n">
-        <v>7117977</v>
+        <v>7117960</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458374</v>
+        <v>128458373</v>
       </c>
       <c r="B51" t="n">
         <v>80135</v>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679493</v>
+        <v>679404</v>
       </c>
       <c r="R51" t="n">
-        <v>7118012</v>
+        <v>7117977</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458388</v>
+        <v>128458374</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679456</v>
+        <v>679493</v>
       </c>
       <c r="R52" t="n">
-        <v>7118056</v>
+        <v>7118012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458342</v>
+        <v>128458388</v>
       </c>
       <c r="B53" t="n">
-        <v>56864</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679446</v>
+        <v>679456</v>
       </c>
       <c r="R53" t="n">
-        <v>7117918</v>
+        <v>7118056</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,32 +6252,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128458692</v>
+        <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>88761</v>
+        <v>80164</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679349</v>
+        <v>679460</v>
       </c>
       <c r="R54" t="n">
-        <v>7117913</v>
+        <v>7118089</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458643</v>
+        <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80164</v>
+        <v>80135</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679460</v>
+        <v>679446</v>
       </c>
       <c r="R55" t="n">
-        <v>7118089</v>
+        <v>7117937</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458368</v>
+        <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80135</v>
+        <v>80164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679446</v>
+        <v>679464</v>
       </c>
       <c r="R56" t="n">
-        <v>7117937</v>
+        <v>7117976</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458351</v>
+        <v>128458358</v>
       </c>
       <c r="B57" t="n">
-        <v>80164</v>
+        <v>57673</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679464</v>
+        <v>679474</v>
       </c>
       <c r="R57" t="n">
-        <v>7117976</v>
+        <v>7117950</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,6 +6614,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6640,32 +6645,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B58" t="n">
-        <v>57673</v>
+        <v>80164</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6675,10 +6680,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R58" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6711,11 +6716,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458350</v>
+        <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>80164</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679446</v>
+        <v>679369</v>
       </c>
       <c r="R59" t="n">
-        <v>7117860</v>
+        <v>7118112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
         <v>79032</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>58043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R61" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7033,45 +7033,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128458378</v>
+        <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>58043</v>
+        <v>80135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>679383</v>
+        <v>679446</v>
       </c>
       <c r="R62" t="n">
-        <v>7117814</v>
+        <v>7117860</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7112,8 +7115,24 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7130,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458367</v>
+        <v>128458680</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7141,37 +7160,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679446</v>
+        <v>679472</v>
       </c>
       <c r="R63" t="n">
-        <v>7117860</v>
+        <v>7118058</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7212,24 +7228,8 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7246,10 +7246,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458353</v>
+        <v>128458366</v>
       </c>
       <c r="B64" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7257,21 +7257,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679512</v>
+        <v>679455</v>
       </c>
       <c r="R64" t="n">
-        <v>7118001</v>
+        <v>7117858</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7317,11 +7317,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7348,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458680</v>
+        <v>128458663</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7359,21 +7354,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7383,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679472</v>
+        <v>679446</v>
       </c>
       <c r="R65" t="n">
-        <v>7118058</v>
+        <v>7118101</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7445,32 +7440,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458366</v>
+        <v>128458375</v>
       </c>
       <c r="B66" t="n">
-        <v>80135</v>
+        <v>80171</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7480,10 +7475,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679455</v>
+        <v>679437</v>
       </c>
       <c r="R66" t="n">
-        <v>7117858</v>
+        <v>7117961</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7542,10 +7537,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458663</v>
+        <v>128458353</v>
       </c>
       <c r="B67" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7553,21 +7548,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7577,10 +7572,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679446</v>
+        <v>679512</v>
       </c>
       <c r="R67" t="n">
-        <v>7118101</v>
+        <v>7118001</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7613,6 +7608,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7639,32 +7639,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458375</v>
+        <v>128458674</v>
       </c>
       <c r="B68" t="n">
-        <v>80171</v>
+        <v>79032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679437</v>
+        <v>679408</v>
       </c>
       <c r="R68" t="n">
-        <v>7117961</v>
+        <v>7117925</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,7 +7736,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128458674</v>
+        <v>128458382</v>
       </c>
       <c r="B69" t="n">
         <v>79032</v>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>679408</v>
+        <v>679440</v>
       </c>
       <c r="R69" t="n">
-        <v>7117925</v>
+        <v>7117885</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7809,12 +7809,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7833,7 +7839,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458382</v>
+        <v>128458672</v>
       </c>
       <c r="B70" t="n">
         <v>79032</v>
@@ -7868,10 +7874,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679440</v>
+        <v>679298</v>
       </c>
       <c r="R70" t="n">
-        <v>7117885</v>
+        <v>7118058</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7906,18 +7912,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458672</v>
+        <v>128458370</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7971,10 +7971,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679298</v>
+        <v>679433</v>
       </c>
       <c r="R71" t="n">
-        <v>7118058</v>
+        <v>7117926</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8033,10 +8033,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458370</v>
+        <v>128458681</v>
       </c>
       <c r="B72" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8044,21 +8044,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679433</v>
+        <v>679506</v>
       </c>
       <c r="R72" t="n">
-        <v>7117926</v>
+        <v>7118062</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458681</v>
+        <v>128458664</v>
       </c>
       <c r="B73" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8141,21 +8141,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679506</v>
+        <v>679459</v>
       </c>
       <c r="R73" t="n">
-        <v>7118062</v>
+        <v>7118087</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8227,10 +8227,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458664</v>
+        <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8238,21 +8238,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679459</v>
+        <v>679436</v>
       </c>
       <c r="R74" t="n">
-        <v>7118087</v>
+        <v>7118086</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,32 +8324,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458671</v>
+        <v>128458642</v>
       </c>
       <c r="B75" t="n">
-        <v>79032</v>
+        <v>80164</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679436</v>
+        <v>679445</v>
       </c>
       <c r="R75" t="n">
-        <v>7118086</v>
+        <v>7118102</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458642</v>
+        <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>80164</v>
+        <v>79032</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679445</v>
+        <v>679512</v>
       </c>
       <c r="R76" t="n">
-        <v>7118102</v>
+        <v>7118001</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8518,7 +8518,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458389</v>
+        <v>128458675</v>
       </c>
       <c r="B77" t="n">
         <v>79032</v>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679512</v>
+        <v>679390</v>
       </c>
       <c r="R77" t="n">
-        <v>7118001</v>
+        <v>7118002</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,32 +8615,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458675</v>
+        <v>128458349</v>
       </c>
       <c r="B78" t="n">
-        <v>79032</v>
+        <v>80164</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679390</v>
+        <v>679455</v>
       </c>
       <c r="R78" t="n">
-        <v>7118002</v>
+        <v>7117858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,7 +8712,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458349</v>
+        <v>128458641</v>
       </c>
       <c r="B79" t="n">
         <v>80164</v>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679455</v>
+        <v>679393</v>
       </c>
       <c r="R79" t="n">
-        <v>7117858</v>
+        <v>7118025</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8809,32 +8809,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458641</v>
+        <v>128458645</v>
       </c>
       <c r="B80" t="n">
-        <v>80164</v>
+        <v>57670</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679393</v>
+        <v>679307</v>
       </c>
       <c r="R80" t="n">
-        <v>7118025</v>
+        <v>7117932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8906,10 +8906,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458645</v>
+        <v>128458638</v>
       </c>
       <c r="B81" t="n">
-        <v>57670</v>
+        <v>79064</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8917,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679307</v>
+        <v>679347</v>
       </c>
       <c r="R81" t="n">
-        <v>7117932</v>
+        <v>7117856</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,6 +8985,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9003,32 +9004,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458638</v>
+        <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>79064</v>
+        <v>58043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679347</v>
+        <v>679279</v>
       </c>
       <c r="R82" t="n">
-        <v>7117856</v>
+        <v>7118000</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9082,7 +9083,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9101,32 +9101,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128458377</v>
+        <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>58043</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>679279</v>
+        <v>679389</v>
       </c>
       <c r="R83" t="n">
-        <v>7118000</v>
+        <v>7117937</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9186,22 +9186,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128472161</v>
+        <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>80135</v>
+        <v>88761</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9209,21 +9209,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>679389</v>
+        <v>679407</v>
       </c>
       <c r="R84" t="n">
-        <v>7117937</v>
+        <v>7117843</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9295,10 +9295,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128472175</v>
+        <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>88761</v>
+        <v>80135</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9306,21 +9306,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9330,10 +9330,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>679407</v>
+        <v>679384</v>
       </c>
       <c r="R85" t="n">
-        <v>7117843</v>
+        <v>7118115</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9389,103 +9389,6 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>128472160</v>
-      </c>
-      <c r="B86" t="n">
-        <v>80135</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Gålgoberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>679384</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7118115</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Felix Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128458658</v>
       </c>
       <c r="B24" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>128458648</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458356</v>
+        <v>128458381</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679480</v>
+        <v>679414</v>
       </c>
       <c r="R27" t="n">
-        <v>7117930</v>
+        <v>7117929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,6 +3698,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3716,10 +3717,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458381</v>
+        <v>128458673</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,10 +3752,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679414</v>
+        <v>679328</v>
       </c>
       <c r="R28" t="n">
-        <v>7117929</v>
+        <v>7117932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3789,18 +3790,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3819,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458673</v>
+        <v>128458365</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3830,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3854,10 +3849,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679328</v>
+        <v>679464</v>
       </c>
       <c r="R29" t="n">
-        <v>7117932</v>
+        <v>7117976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3898,6 +3893,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3916,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458365</v>
+        <v>128458356</v>
       </c>
       <c r="B30" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,21 +3923,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3951,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679464</v>
+        <v>679480</v>
       </c>
       <c r="R30" t="n">
-        <v>7117976</v>
+        <v>7117930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3989,13 +3985,17 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>128458344</v>
       </c>
       <c r="B31" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>91371</v>
+        <v>91463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>128458369</v>
       </c>
       <c r="B38" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128458640</v>
       </c>
       <c r="B40" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>128458364</v>
       </c>
       <c r="B41" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128458677</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128458384</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128458661</v>
       </c>
       <c r="B46" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>128458371</v>
       </c>
       <c r="B47" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458342</v>
+        <v>128458662</v>
       </c>
       <c r="B48" t="n">
-        <v>56864</v>
+        <v>80188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679446</v>
+        <v>679403</v>
       </c>
       <c r="R48" t="n">
-        <v>7117918</v>
+        <v>7117960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458692</v>
+        <v>128458373</v>
       </c>
       <c r="B49" t="n">
-        <v>88761</v>
+        <v>80188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679349</v>
+        <v>679404</v>
       </c>
       <c r="R49" t="n">
-        <v>7117913</v>
+        <v>7117977</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458662</v>
+        <v>128458374</v>
       </c>
       <c r="B50" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679403</v>
+        <v>679493</v>
       </c>
       <c r="R50" t="n">
-        <v>7117960</v>
+        <v>7118012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458373</v>
+        <v>128458388</v>
       </c>
       <c r="B51" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679404</v>
+        <v>679456</v>
       </c>
       <c r="R51" t="n">
-        <v>7117977</v>
+        <v>7118056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458374</v>
+        <v>128458342</v>
       </c>
       <c r="B52" t="n">
-        <v>80135</v>
+        <v>56876</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679493</v>
+        <v>679446</v>
       </c>
       <c r="R52" t="n">
-        <v>7118012</v>
+        <v>7117918</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,10 +6155,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458388</v>
+        <v>128458692</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>88853</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,21 +6166,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679456</v>
+        <v>679349</v>
       </c>
       <c r="R53" t="n">
-        <v>7118056</v>
+        <v>7117913</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,7 +6255,7 @@
         <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>128458358</v>
       </c>
       <c r="B57" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128458350</v>
       </c>
       <c r="B58" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458678</v>
+        <v>128458378</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>58055</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679369</v>
+        <v>679383</v>
       </c>
       <c r="R59" t="n">
-        <v>7118112</v>
+        <v>7117814</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458387</v>
+        <v>128458678</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679461</v>
+        <v>679369</v>
       </c>
       <c r="R60" t="n">
-        <v>7117988</v>
+        <v>7118112</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B61" t="n">
-        <v>58043</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R61" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>128458680</v>
       </c>
       <c r="B63" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>128458366</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>128458663</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128458375</v>
       </c>
       <c r="B66" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>128458353</v>
       </c>
       <c r="B67" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>128458674</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>128458382</v>
       </c>
       <c r="B69" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>128458672</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>128458370</v>
       </c>
       <c r="B71" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>128458681</v>
       </c>
       <c r="B72" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>128458664</v>
       </c>
       <c r="B73" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>128458642</v>
       </c>
       <c r="B75" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>128458675</v>
       </c>
       <c r="B77" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128458349</v>
       </c>
       <c r="B78" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128458641</v>
       </c>
       <c r="B79" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458645</v>
+        <v>128458638</v>
       </c>
       <c r="B80" t="n">
-        <v>57670</v>
+        <v>79115</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679307</v>
+        <v>679347</v>
       </c>
       <c r="R80" t="n">
-        <v>7117932</v>
+        <v>7117856</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,6 +8888,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8906,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>79064</v>
+        <v>57682</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8918,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R81" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,7 +8986,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458644</v>
+        <v>128458679</v>
       </c>
       <c r="B34" t="n">
-        <v>91463</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679456</v>
+        <v>679434</v>
       </c>
       <c r="R34" t="n">
-        <v>7118095</v>
+        <v>7118112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458679</v>
+        <v>128458372</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679434</v>
+        <v>679409</v>
       </c>
       <c r="R35" t="n">
-        <v>7118112</v>
+        <v>7117952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458372</v>
+        <v>128458386</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679409</v>
+        <v>679411</v>
       </c>
       <c r="R36" t="n">
-        <v>7117952</v>
+        <v>7117970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458386</v>
+        <v>128458369</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679411</v>
+        <v>679437</v>
       </c>
       <c r="R37" t="n">
-        <v>7117970</v>
+        <v>7117961</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458369</v>
+        <v>128458659</v>
       </c>
       <c r="B38" t="n">
         <v>80188</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679437</v>
+        <v>679419</v>
       </c>
       <c r="R38" t="n">
-        <v>7117961</v>
+        <v>7118102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458659</v>
+        <v>128458644</v>
       </c>
       <c r="B39" t="n">
-        <v>80188</v>
+        <v>91463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679419</v>
+        <v>679456</v>
       </c>
       <c r="R39" t="n">
-        <v>7118102</v>
+        <v>7118095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458342</v>
+        <v>128458692</v>
       </c>
       <c r="B52" t="n">
-        <v>56876</v>
+        <v>88853</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679446</v>
+        <v>679349</v>
       </c>
       <c r="R52" t="n">
-        <v>7117918</v>
+        <v>7117913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458692</v>
+        <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>88853</v>
+        <v>56876</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679349</v>
+        <v>679446</v>
       </c>
       <c r="R53" t="n">
-        <v>7117913</v>
+        <v>7117918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458378</v>
+        <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>58055</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679383</v>
+        <v>679369</v>
       </c>
       <c r="R59" t="n">
-        <v>7117814</v>
+        <v>7118112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
         <v>79083</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>58055</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R61" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B80" t="n">
-        <v>79115</v>
+        <v>57682</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R80" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,7 +8888,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8907,10 +8906,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458645</v>
+        <v>128458638</v>
       </c>
       <c r="B81" t="n">
-        <v>57682</v>
+        <v>79115</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8918,21 +8917,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8942,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679307</v>
+        <v>679347</v>
       </c>
       <c r="R81" t="n">
-        <v>7117932</v>
+        <v>7117856</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8986,6 +8985,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458679</v>
+        <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>91463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679434</v>
+        <v>679456</v>
       </c>
       <c r="R34" t="n">
-        <v>7118112</v>
+        <v>7118095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458372</v>
+        <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679409</v>
+        <v>679434</v>
       </c>
       <c r="R35" t="n">
-        <v>7117952</v>
+        <v>7118112</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458386</v>
+        <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679411</v>
+        <v>679409</v>
       </c>
       <c r="R36" t="n">
-        <v>7117970</v>
+        <v>7117952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458369</v>
+        <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679437</v>
+        <v>679411</v>
       </c>
       <c r="R37" t="n">
-        <v>7117961</v>
+        <v>7117970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458659</v>
+        <v>128458369</v>
       </c>
       <c r="B38" t="n">
         <v>80188</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679419</v>
+        <v>679437</v>
       </c>
       <c r="R38" t="n">
-        <v>7118102</v>
+        <v>7117961</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458644</v>
+        <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>91463</v>
+        <v>80188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679456</v>
+        <v>679419</v>
       </c>
       <c r="R39" t="n">
-        <v>7118095</v>
+        <v>7118102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458662</v>
+        <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>80188</v>
+        <v>88853</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679403</v>
+        <v>679349</v>
       </c>
       <c r="R48" t="n">
-        <v>7117960</v>
+        <v>7117913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,32 +5767,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458373</v>
+        <v>128458342</v>
       </c>
       <c r="B49" t="n">
-        <v>80188</v>
+        <v>56876</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679404</v>
+        <v>679446</v>
       </c>
       <c r="R49" t="n">
-        <v>7117977</v>
+        <v>7117918</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458374</v>
+        <v>128458662</v>
       </c>
       <c r="B50" t="n">
         <v>80188</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679493</v>
+        <v>679403</v>
       </c>
       <c r="R50" t="n">
-        <v>7118012</v>
+        <v>7117960</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458388</v>
+        <v>128458373</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679456</v>
+        <v>679404</v>
       </c>
       <c r="R51" t="n">
-        <v>7118056</v>
+        <v>7117977</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458692</v>
+        <v>128458374</v>
       </c>
       <c r="B52" t="n">
-        <v>88853</v>
+        <v>80188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679349</v>
+        <v>679493</v>
       </c>
       <c r="R52" t="n">
-        <v>7117913</v>
+        <v>7118012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458342</v>
+        <v>128458388</v>
       </c>
       <c r="B53" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679446</v>
+        <v>679456</v>
       </c>
       <c r="R53" t="n">
-        <v>7117918</v>
+        <v>7118056</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>80217</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R57" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,11 +6614,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6645,32 +6640,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458350</v>
+        <v>128458358</v>
       </c>
       <c r="B58" t="n">
-        <v>80217</v>
+        <v>57685</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6680,10 +6675,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679446</v>
+        <v>679474</v>
       </c>
       <c r="R58" t="n">
-        <v>7117860</v>
+        <v>7117950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6716,6 +6711,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8906,32 +8906,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458638</v>
+        <v>128458377</v>
       </c>
       <c r="B81" t="n">
-        <v>79115</v>
+        <v>58055</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679347</v>
+        <v>679279</v>
       </c>
       <c r="R81" t="n">
-        <v>7117856</v>
+        <v>7118000</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,7 +8985,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,32 +9003,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B82" t="n">
-        <v>58055</v>
+        <v>79115</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9039,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R82" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9083,6 +9082,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458692</v>
+        <v>128458342</v>
       </c>
       <c r="B48" t="n">
-        <v>88853</v>
+        <v>56876</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679349</v>
+        <v>679446</v>
       </c>
       <c r="R48" t="n">
-        <v>7117913</v>
+        <v>7117918</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,32 +5767,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458342</v>
+        <v>128458692</v>
       </c>
       <c r="B49" t="n">
-        <v>56876</v>
+        <v>88853</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679446</v>
+        <v>679349</v>
       </c>
       <c r="R49" t="n">
-        <v>7117918</v>
+        <v>7117913</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128458658</v>
       </c>
       <c r="B24" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>128458648</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>128458381</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>128458673</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128458365</v>
       </c>
       <c r="B29" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128458356</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>128458344</v>
       </c>
       <c r="B31" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>91463</v>
+        <v>91475</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>128458369</v>
       </c>
       <c r="B38" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128458640</v>
       </c>
       <c r="B40" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>128458364</v>
       </c>
       <c r="B41" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128458677</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128458384</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128458661</v>
       </c>
       <c r="B46" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>128458371</v>
       </c>
       <c r="B47" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458342</v>
+        <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>56876</v>
+        <v>88865</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679446</v>
+        <v>679349</v>
       </c>
       <c r="R48" t="n">
-        <v>7117918</v>
+        <v>7117913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B49" t="n">
-        <v>88853</v>
+        <v>80192</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R49" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458662</v>
+        <v>128458373</v>
       </c>
       <c r="B50" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679403</v>
+        <v>679404</v>
       </c>
       <c r="R50" t="n">
-        <v>7117960</v>
+        <v>7117977</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458373</v>
+        <v>128458374</v>
       </c>
       <c r="B51" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679404</v>
+        <v>679493</v>
       </c>
       <c r="R51" t="n">
-        <v>7117977</v>
+        <v>7118012</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458374</v>
+        <v>128458388</v>
       </c>
       <c r="B52" t="n">
-        <v>80188</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679493</v>
+        <v>679456</v>
       </c>
       <c r="R52" t="n">
-        <v>7118012</v>
+        <v>7118056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458388</v>
+        <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>56880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679456</v>
+        <v>679446</v>
       </c>
       <c r="R53" t="n">
-        <v>7118056</v>
+        <v>7117918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,7 +6255,7 @@
         <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>128458350</v>
       </c>
       <c r="B57" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>128458358</v>
       </c>
       <c r="B58" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>128458387</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>128458680</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>128458366</v>
       </c>
       <c r="B64" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>128458663</v>
       </c>
       <c r="B65" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128458375</v>
       </c>
       <c r="B66" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>128458353</v>
       </c>
       <c r="B67" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>128458674</v>
       </c>
       <c r="B68" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>128458382</v>
       </c>
       <c r="B69" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>128458672</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>128458370</v>
       </c>
       <c r="B71" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>128458681</v>
       </c>
       <c r="B72" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>128458664</v>
       </c>
       <c r="B73" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>128458642</v>
       </c>
       <c r="B75" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>128458675</v>
       </c>
       <c r="B77" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128458349</v>
       </c>
       <c r="B78" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128458641</v>
       </c>
       <c r="B79" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8809,27 +8809,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B80" t="n">
-        <v>57682</v>
+        <v>58059</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R80" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8906,32 +8906,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B81" t="n">
-        <v>58055</v>
+        <v>79119</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R81" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,6 +8985,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9003,10 +9004,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B82" t="n">
-        <v>79115</v>
+        <v>57686</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9014,21 +9015,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R82" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9082,7 +9083,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B48" t="n">
-        <v>88865</v>
+        <v>80192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R48" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458662</v>
+        <v>128458373</v>
       </c>
       <c r="B49" t="n">
         <v>80192</v>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679403</v>
+        <v>679404</v>
       </c>
       <c r="R49" t="n">
-        <v>7117960</v>
+        <v>7117977</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458373</v>
+        <v>128458374</v>
       </c>
       <c r="B50" t="n">
         <v>80192</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679404</v>
+        <v>679493</v>
       </c>
       <c r="R50" t="n">
-        <v>7117977</v>
+        <v>7118012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458374</v>
+        <v>128458388</v>
       </c>
       <c r="B51" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679493</v>
+        <v>679456</v>
       </c>
       <c r="R51" t="n">
-        <v>7118012</v>
+        <v>7118056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458388</v>
+        <v>128458342</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>56880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679456</v>
+        <v>679446</v>
       </c>
       <c r="R52" t="n">
-        <v>7118056</v>
+        <v>7117918</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458342</v>
+        <v>128458692</v>
       </c>
       <c r="B53" t="n">
-        <v>56880</v>
+        <v>88865</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679446</v>
+        <v>679349</v>
       </c>
       <c r="R53" t="n">
-        <v>7117918</v>
+        <v>7117913</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128458658</v>
       </c>
       <c r="B24" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>128458381</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>128458673</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128458365</v>
       </c>
       <c r="B29" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>91475</v>
+        <v>91477</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>128458369</v>
       </c>
       <c r="B38" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128458640</v>
       </c>
       <c r="B40" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>128458364</v>
       </c>
       <c r="B41" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128458677</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458340</v>
+        <v>128458661</v>
       </c>
       <c r="B44" t="n">
-        <v>79706</v>
+        <v>80194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679488</v>
+        <v>679395</v>
       </c>
       <c r="R44" t="n">
-        <v>7118028</v>
+        <v>7117956</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458384</v>
+        <v>128458371</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679443</v>
+        <v>679394</v>
       </c>
       <c r="R45" t="n">
-        <v>7117919</v>
+        <v>7117935</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,18 +5446,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5476,10 +5470,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458661</v>
+        <v>128458340</v>
       </c>
       <c r="B46" t="n">
-        <v>80192</v>
+        <v>79708</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5487,21 +5481,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5511,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679395</v>
+        <v>679488</v>
       </c>
       <c r="R46" t="n">
-        <v>7117956</v>
+        <v>7118028</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5573,10 +5567,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458371</v>
+        <v>128458384</v>
       </c>
       <c r="B47" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5584,21 +5578,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5608,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679394</v>
+        <v>679443</v>
       </c>
       <c r="R47" t="n">
-        <v>7117935</v>
+        <v>7117919</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,12 +5640,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458662</v>
+        <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>80192</v>
+        <v>88867</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679403</v>
+        <v>679349</v>
       </c>
       <c r="R48" t="n">
-        <v>7117960</v>
+        <v>7117913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458373</v>
+        <v>128458662</v>
       </c>
       <c r="B49" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679404</v>
+        <v>679403</v>
       </c>
       <c r="R49" t="n">
-        <v>7117977</v>
+        <v>7117960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458374</v>
+        <v>128458373</v>
       </c>
       <c r="B50" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679493</v>
+        <v>679404</v>
       </c>
       <c r="R50" t="n">
-        <v>7118012</v>
+        <v>7117977</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458388</v>
+        <v>128458374</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679456</v>
+        <v>679493</v>
       </c>
       <c r="R51" t="n">
-        <v>7118056</v>
+        <v>7118012</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458342</v>
+        <v>128458388</v>
       </c>
       <c r="B52" t="n">
-        <v>56880</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679446</v>
+        <v>679456</v>
       </c>
       <c r="R52" t="n">
-        <v>7117918</v>
+        <v>7118056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458692</v>
+        <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>88865</v>
+        <v>56880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679349</v>
+        <v>679446</v>
       </c>
       <c r="R53" t="n">
-        <v>7117913</v>
+        <v>7117918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,7 +6255,7 @@
         <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>128458350</v>
       </c>
       <c r="B57" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458678</v>
+        <v>128458378</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>58059</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679369</v>
+        <v>679383</v>
       </c>
       <c r="R59" t="n">
-        <v>7118112</v>
+        <v>7117814</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458387</v>
+        <v>128458678</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679461</v>
+        <v>679369</v>
       </c>
       <c r="R60" t="n">
-        <v>7117988</v>
+        <v>7118112</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B61" t="n">
-        <v>58059</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R61" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458680</v>
+        <v>128458663</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679472</v>
+        <v>679446</v>
       </c>
       <c r="R63" t="n">
-        <v>7118058</v>
+        <v>7118101</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458366</v>
+        <v>128458375</v>
       </c>
       <c r="B64" t="n">
-        <v>80192</v>
+        <v>80230</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679455</v>
+        <v>679437</v>
       </c>
       <c r="R64" t="n">
-        <v>7117858</v>
+        <v>7117961</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458663</v>
+        <v>128458680</v>
       </c>
       <c r="B65" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7354,21 +7354,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679446</v>
+        <v>679472</v>
       </c>
       <c r="R65" t="n">
-        <v>7118101</v>
+        <v>7118058</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458375</v>
+        <v>128458366</v>
       </c>
       <c r="B66" t="n">
-        <v>80228</v>
+        <v>80194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679437</v>
+        <v>679455</v>
       </c>
       <c r="R66" t="n">
-        <v>7117961</v>
+        <v>7117858</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
         <v>128458674</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>128458382</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>128458672</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>128458370</v>
       </c>
       <c r="B71" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>128458681</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>128458664</v>
       </c>
       <c r="B73" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>128458642</v>
       </c>
       <c r="B75" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>128458675</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128458349</v>
       </c>
       <c r="B78" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128458641</v>
       </c>
       <c r="B79" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8809,32 +8809,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B80" t="n">
-        <v>58059</v>
+        <v>79121</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R80" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,6 +8888,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8906,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>79119</v>
+        <v>57686</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8918,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R81" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,7 +8986,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,27 +9004,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R82" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458644</v>
+        <v>128458659</v>
       </c>
       <c r="B34" t="n">
-        <v>91477</v>
+        <v>80194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679456</v>
+        <v>679419</v>
       </c>
       <c r="R34" t="n">
-        <v>7118095</v>
+        <v>7118102</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458659</v>
+        <v>128458644</v>
       </c>
       <c r="B39" t="n">
-        <v>80194</v>
+        <v>91477</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679419</v>
+        <v>679456</v>
       </c>
       <c r="R39" t="n">
-        <v>7118102</v>
+        <v>7118095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458640</v>
+        <v>128458364</v>
       </c>
       <c r="B40" t="n">
-        <v>80223</v>
+        <v>80194</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679458</v>
+        <v>679421</v>
       </c>
       <c r="R40" t="n">
-        <v>7118097</v>
+        <v>7117929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4966,6 +4966,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4984,10 +4985,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458364</v>
+        <v>128458677</v>
       </c>
       <c r="B41" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,21 +4996,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +5020,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679421</v>
+        <v>679355</v>
       </c>
       <c r="R41" t="n">
-        <v>7117929</v>
+        <v>7118031</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5063,7 +5064,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458677</v>
+        <v>128458660</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679355</v>
+        <v>679372</v>
       </c>
       <c r="R42" t="n">
-        <v>7118031</v>
+        <v>7117955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5179,32 +5179,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458660</v>
+        <v>128458640</v>
       </c>
       <c r="B43" t="n">
-        <v>80194</v>
+        <v>80223</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679372</v>
+        <v>679458</v>
       </c>
       <c r="R43" t="n">
-        <v>7117955</v>
+        <v>7118097</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458661</v>
+        <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>80194</v>
+        <v>79708</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679395</v>
+        <v>679488</v>
       </c>
       <c r="R44" t="n">
-        <v>7117956</v>
+        <v>7118028</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458371</v>
+        <v>128458384</v>
       </c>
       <c r="B45" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679394</v>
+        <v>679443</v>
       </c>
       <c r="R45" t="n">
-        <v>7117935</v>
+        <v>7117919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,12 +5446,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5470,10 +5476,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458340</v>
+        <v>128458661</v>
       </c>
       <c r="B46" t="n">
-        <v>79708</v>
+        <v>80194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5481,21 +5487,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5505,10 +5511,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679488</v>
+        <v>679395</v>
       </c>
       <c r="R46" t="n">
-        <v>7118028</v>
+        <v>7117956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5567,10 +5573,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458384</v>
+        <v>128458371</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5578,21 +5584,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5608,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679443</v>
+        <v>679394</v>
       </c>
       <c r="R47" t="n">
-        <v>7117919</v>
+        <v>7117935</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5640,18 +5646,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B48" t="n">
-        <v>88867</v>
+        <v>80194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R48" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458662</v>
+        <v>128458373</v>
       </c>
       <c r="B49" t="n">
         <v>80194</v>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679403</v>
+        <v>679404</v>
       </c>
       <c r="R49" t="n">
-        <v>7117960</v>
+        <v>7117977</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458373</v>
+        <v>128458374</v>
       </c>
       <c r="B50" t="n">
         <v>80194</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679404</v>
+        <v>679493</v>
       </c>
       <c r="R50" t="n">
-        <v>7117977</v>
+        <v>7118012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458374</v>
+        <v>128458388</v>
       </c>
       <c r="B51" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679493</v>
+        <v>679456</v>
       </c>
       <c r="R51" t="n">
-        <v>7118012</v>
+        <v>7118056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458388</v>
+        <v>128458692</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>88867</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679456</v>
+        <v>679349</v>
       </c>
       <c r="R52" t="n">
-        <v>7118056</v>
+        <v>7117913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458378</v>
+        <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>58059</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679383</v>
+        <v>679369</v>
       </c>
       <c r="R59" t="n">
-        <v>7117814</v>
+        <v>7118112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
         <v>79089</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>58059</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R61" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458663</v>
+        <v>128458680</v>
       </c>
       <c r="B63" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679446</v>
+        <v>679472</v>
       </c>
       <c r="R63" t="n">
-        <v>7118101</v>
+        <v>7118058</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458375</v>
+        <v>128458366</v>
       </c>
       <c r="B64" t="n">
-        <v>80230</v>
+        <v>80194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679437</v>
+        <v>679455</v>
       </c>
       <c r="R64" t="n">
-        <v>7117961</v>
+        <v>7117858</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458680</v>
+        <v>128458663</v>
       </c>
       <c r="B65" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7354,21 +7354,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679472</v>
+        <v>679446</v>
       </c>
       <c r="R65" t="n">
-        <v>7118058</v>
+        <v>7118101</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458366</v>
+        <v>128458375</v>
       </c>
       <c r="B66" t="n">
-        <v>80194</v>
+        <v>80230</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679455</v>
+        <v>679437</v>
       </c>
       <c r="R66" t="n">
-        <v>7117858</v>
+        <v>7117961</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8324,32 +8324,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458642</v>
+        <v>128458389</v>
       </c>
       <c r="B75" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679445</v>
+        <v>679512</v>
       </c>
       <c r="R75" t="n">
-        <v>7118102</v>
+        <v>7118001</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458389</v>
+        <v>128458642</v>
       </c>
       <c r="B76" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679512</v>
+        <v>679445</v>
       </c>
       <c r="R76" t="n">
-        <v>7118001</v>
+        <v>7118102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -4111,27 +4111,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458670</v>
+        <v>128458399</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679402</v>
+        <v>679418</v>
       </c>
       <c r="R32" t="n">
-        <v>7117958</v>
+        <v>7117932</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4208,27 +4208,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458399</v>
+        <v>128458670</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679418</v>
+        <v>679402</v>
       </c>
       <c r="R33" t="n">
-        <v>7117932</v>
+        <v>7117958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4305,10 +4305,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458659</v>
+        <v>128458679</v>
       </c>
       <c r="B34" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,21 +4316,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679419</v>
+        <v>679434</v>
       </c>
       <c r="R34" t="n">
-        <v>7118102</v>
+        <v>7118112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458679</v>
+        <v>128458372</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679434</v>
+        <v>679409</v>
       </c>
       <c r="R35" t="n">
-        <v>7118112</v>
+        <v>7117952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458372</v>
+        <v>128458386</v>
       </c>
       <c r="B36" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679409</v>
+        <v>679411</v>
       </c>
       <c r="R36" t="n">
-        <v>7117952</v>
+        <v>7117970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458386</v>
+        <v>128458369</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679411</v>
+        <v>679437</v>
       </c>
       <c r="R37" t="n">
-        <v>7117970</v>
+        <v>7117961</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458369</v>
+        <v>128458659</v>
       </c>
       <c r="B38" t="n">
         <v>80194</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679437</v>
+        <v>679419</v>
       </c>
       <c r="R38" t="n">
-        <v>7117961</v>
+        <v>7118102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458364</v>
+        <v>128458640</v>
       </c>
       <c r="B40" t="n">
-        <v>80194</v>
+        <v>80223</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679421</v>
+        <v>679458</v>
       </c>
       <c r="R40" t="n">
-        <v>7117929</v>
+        <v>7118097</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4966,7 +4966,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4985,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458677</v>
+        <v>128458364</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4996,21 +4995,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5020,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679355</v>
+        <v>679421</v>
       </c>
       <c r="R41" t="n">
-        <v>7118031</v>
+        <v>7117929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5064,6 +5063,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458660</v>
+        <v>128458677</v>
       </c>
       <c r="B42" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679372</v>
+        <v>679355</v>
       </c>
       <c r="R42" t="n">
-        <v>7117955</v>
+        <v>7118031</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5179,32 +5179,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458640</v>
+        <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80223</v>
+        <v>80194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679458</v>
+        <v>679372</v>
       </c>
       <c r="R43" t="n">
-        <v>7118097</v>
+        <v>7117955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458350</v>
+        <v>128458358</v>
       </c>
       <c r="B57" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679446</v>
+        <v>679474</v>
       </c>
       <c r="R57" t="n">
-        <v>7117860</v>
+        <v>7117950</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,6 +6614,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6640,32 +6645,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6675,10 +6680,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R58" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6711,11 +6716,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458678</v>
+        <v>128458378</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>58059</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679369</v>
+        <v>679383</v>
       </c>
       <c r="R59" t="n">
-        <v>7118112</v>
+        <v>7117814</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458387</v>
+        <v>128458678</v>
       </c>
       <c r="B60" t="n">
         <v>79089</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679461</v>
+        <v>679369</v>
       </c>
       <c r="R60" t="n">
-        <v>7117988</v>
+        <v>7118112</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B61" t="n">
-        <v>58059</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R61" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8907,27 +8907,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B81" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R81" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9004,27 +9004,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458377</v>
+        <v>128458645</v>
       </c>
       <c r="B82" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679279</v>
+        <v>679307</v>
       </c>
       <c r="R82" t="n">
-        <v>7118000</v>
+        <v>7117932</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -4111,27 +4111,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458399</v>
+        <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679418</v>
+        <v>679402</v>
       </c>
       <c r="R32" t="n">
-        <v>7117932</v>
+        <v>7117958</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4208,27 +4208,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458670</v>
+        <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679402</v>
+        <v>679418</v>
       </c>
       <c r="R33" t="n">
-        <v>7117958</v>
+        <v>7117932</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458679</v>
+        <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>91478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679434</v>
+        <v>679456</v>
       </c>
       <c r="R34" t="n">
-        <v>7118112</v>
+        <v>7118095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458372</v>
+        <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679409</v>
+        <v>679434</v>
       </c>
       <c r="R35" t="n">
-        <v>7117952</v>
+        <v>7118112</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458369</v>
+        <v>128458372</v>
       </c>
       <c r="B37" t="n">
         <v>80194</v>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679437</v>
+        <v>679409</v>
       </c>
       <c r="R37" t="n">
-        <v>7117961</v>
+        <v>7117952</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458659</v>
+        <v>128458369</v>
       </c>
       <c r="B38" t="n">
         <v>80194</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679419</v>
+        <v>679437</v>
       </c>
       <c r="R38" t="n">
-        <v>7118102</v>
+        <v>7117961</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458644</v>
+        <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>91477</v>
+        <v>80194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679456</v>
+        <v>679419</v>
       </c>
       <c r="R39" t="n">
-        <v>7118095</v>
+        <v>7118102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458640</v>
+        <v>128458677</v>
       </c>
       <c r="B40" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679458</v>
+        <v>679355</v>
       </c>
       <c r="R40" t="n">
-        <v>7118097</v>
+        <v>7118031</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4984,32 +4984,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458364</v>
+        <v>128458640</v>
       </c>
       <c r="B41" t="n">
-        <v>80194</v>
+        <v>80223</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679421</v>
+        <v>679458</v>
       </c>
       <c r="R41" t="n">
-        <v>7117929</v>
+        <v>7118097</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5063,7 +5063,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5082,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458677</v>
+        <v>128458364</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,21 +5092,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5117,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679355</v>
+        <v>679421</v>
       </c>
       <c r="R42" t="n">
-        <v>7118031</v>
+        <v>7117929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5161,6 +5160,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458340</v>
+        <v>128458384</v>
       </c>
       <c r="B44" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679488</v>
+        <v>679443</v>
       </c>
       <c r="R44" t="n">
-        <v>7118028</v>
+        <v>7117919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5349,12 +5349,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5373,10 +5379,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458384</v>
+        <v>128458340</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5390,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5414,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679443</v>
+        <v>679488</v>
       </c>
       <c r="R45" t="n">
-        <v>7117919</v>
+        <v>7118028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,18 +5452,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458388</v>
+        <v>128458692</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>88867</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679456</v>
+        <v>679349</v>
       </c>
       <c r="R51" t="n">
-        <v>7118056</v>
+        <v>7117913</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458692</v>
+        <v>128458388</v>
       </c>
       <c r="B52" t="n">
-        <v>88867</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679349</v>
+        <v>679456</v>
       </c>
       <c r="R52" t="n">
-        <v>7117913</v>
+        <v>7118056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7936,10 +7936,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458370</v>
+        <v>128458681</v>
       </c>
       <c r="B71" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7971,10 +7971,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679433</v>
+        <v>679506</v>
       </c>
       <c r="R71" t="n">
-        <v>7117926</v>
+        <v>7118062</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8033,10 +8033,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458681</v>
+        <v>128458370</v>
       </c>
       <c r="B72" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8044,21 +8044,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679506</v>
+        <v>679433</v>
       </c>
       <c r="R72" t="n">
-        <v>7118062</v>
+        <v>7117926</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B80" t="n">
-        <v>79121</v>
+        <v>57686</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R80" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,7 +8888,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8907,32 +8906,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B81" t="n">
-        <v>58059</v>
+        <v>79121</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8942,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R81" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8986,6 +8985,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,27 +9004,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R82" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458644</v>
+        <v>128458679</v>
       </c>
       <c r="B34" t="n">
-        <v>91478</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679456</v>
+        <v>679434</v>
       </c>
       <c r="R34" t="n">
-        <v>7118095</v>
+        <v>7118112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458679</v>
+        <v>128458386</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679434</v>
+        <v>679411</v>
       </c>
       <c r="R35" t="n">
-        <v>7118112</v>
+        <v>7117970</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458386</v>
+        <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679411</v>
+        <v>679409</v>
       </c>
       <c r="R36" t="n">
-        <v>7117970</v>
+        <v>7117952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458372</v>
+        <v>128458369</v>
       </c>
       <c r="B37" t="n">
         <v>80194</v>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679409</v>
+        <v>679437</v>
       </c>
       <c r="R37" t="n">
-        <v>7117952</v>
+        <v>7117961</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458369</v>
+        <v>128458659</v>
       </c>
       <c r="B38" t="n">
         <v>80194</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679437</v>
+        <v>679419</v>
       </c>
       <c r="R38" t="n">
-        <v>7117961</v>
+        <v>7118102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458659</v>
+        <v>128458644</v>
       </c>
       <c r="B39" t="n">
-        <v>80194</v>
+        <v>91478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679419</v>
+        <v>679456</v>
       </c>
       <c r="R39" t="n">
-        <v>7118102</v>
+        <v>7118095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R57" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,11 +6614,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6645,32 +6640,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458350</v>
+        <v>128458358</v>
       </c>
       <c r="B58" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6680,10 +6675,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679446</v>
+        <v>679474</v>
       </c>
       <c r="R58" t="n">
-        <v>7117860</v>
+        <v>7117950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6716,6 +6711,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128458658</v>
       </c>
       <c r="B24" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>128458648</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>128458381</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>128458673</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128458365</v>
       </c>
       <c r="B29" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128458356</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>128458344</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4111,27 +4111,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458670</v>
+        <v>128458399</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>80256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679402</v>
+        <v>679418</v>
       </c>
       <c r="R32" t="n">
-        <v>7117958</v>
+        <v>7117932</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4208,27 +4208,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458399</v>
+        <v>128458670</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679418</v>
+        <v>679402</v>
       </c>
       <c r="R33" t="n">
-        <v>7117932</v>
+        <v>7117958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458679</v>
+        <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>91505</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679434</v>
+        <v>679456</v>
       </c>
       <c r="R34" t="n">
-        <v>7118112</v>
+        <v>7118095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458386</v>
+        <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679411</v>
+        <v>679434</v>
       </c>
       <c r="R35" t="n">
-        <v>7117970</v>
+        <v>7118112</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458372</v>
+        <v>128458386</v>
       </c>
       <c r="B36" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679409</v>
+        <v>679411</v>
       </c>
       <c r="R36" t="n">
-        <v>7117952</v>
+        <v>7117970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458369</v>
+        <v>128458372</v>
       </c>
       <c r="B37" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679437</v>
+        <v>679409</v>
       </c>
       <c r="R37" t="n">
-        <v>7117961</v>
+        <v>7117952</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458659</v>
+        <v>128458369</v>
       </c>
       <c r="B38" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679419</v>
+        <v>679437</v>
       </c>
       <c r="R38" t="n">
-        <v>7118102</v>
+        <v>7117961</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458644</v>
+        <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>91478</v>
+        <v>80221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679456</v>
+        <v>679419</v>
       </c>
       <c r="R39" t="n">
-        <v>7118095</v>
+        <v>7118102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4890,7 +4890,7 @@
         <v>128458677</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>128458640</v>
       </c>
       <c r="B41" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>128458364</v>
       </c>
       <c r="B42" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458384</v>
+        <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679443</v>
+        <v>679488</v>
       </c>
       <c r="R44" t="n">
-        <v>7117919</v>
+        <v>7118028</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5349,18 +5349,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5379,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458340</v>
+        <v>128458661</v>
       </c>
       <c r="B45" t="n">
-        <v>79708</v>
+        <v>80221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5390,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5414,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679488</v>
+        <v>679395</v>
       </c>
       <c r="R45" t="n">
-        <v>7118028</v>
+        <v>7117956</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5476,10 +5470,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458661</v>
+        <v>128458371</v>
       </c>
       <c r="B46" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5511,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679395</v>
+        <v>679394</v>
       </c>
       <c r="R46" t="n">
-        <v>7117956</v>
+        <v>7117935</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5573,10 +5567,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458371</v>
+        <v>128458384</v>
       </c>
       <c r="B47" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5584,21 +5578,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5608,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679394</v>
+        <v>679443</v>
       </c>
       <c r="R47" t="n">
-        <v>7117935</v>
+        <v>7117919</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,12 +5640,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458662</v>
+        <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>80194</v>
+        <v>88894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679403</v>
+        <v>679349</v>
       </c>
       <c r="R48" t="n">
-        <v>7117960</v>
+        <v>7117913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,32 +5767,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458373</v>
+        <v>128458342</v>
       </c>
       <c r="B49" t="n">
-        <v>80194</v>
+        <v>56907</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679404</v>
+        <v>679446</v>
       </c>
       <c r="R49" t="n">
-        <v>7117977</v>
+        <v>7117918</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458374</v>
+        <v>128458388</v>
       </c>
       <c r="B50" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679493</v>
+        <v>679456</v>
       </c>
       <c r="R50" t="n">
-        <v>7118012</v>
+        <v>7118056</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B51" t="n">
-        <v>88867</v>
+        <v>80221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R51" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458388</v>
+        <v>128458373</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679456</v>
+        <v>679404</v>
       </c>
       <c r="R52" t="n">
-        <v>7118056</v>
+        <v>7117977</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458342</v>
+        <v>128458374</v>
       </c>
       <c r="B53" t="n">
-        <v>56880</v>
+        <v>80221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679446</v>
+        <v>679493</v>
       </c>
       <c r="R53" t="n">
-        <v>7117918</v>
+        <v>7118012</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,7 +6255,7 @@
         <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>128458350</v>
       </c>
       <c r="B57" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>128458358</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458378</v>
+        <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>58059</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679383</v>
+        <v>679369</v>
       </c>
       <c r="R59" t="n">
-        <v>7117814</v>
+        <v>7118112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>58086</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R61" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458680</v>
+        <v>128458366</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679472</v>
+        <v>679455</v>
       </c>
       <c r="R63" t="n">
-        <v>7118058</v>
+        <v>7117858</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7246,10 +7246,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458366</v>
+        <v>128458663</v>
       </c>
       <c r="B64" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679455</v>
+        <v>679446</v>
       </c>
       <c r="R64" t="n">
-        <v>7117858</v>
+        <v>7118101</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458663</v>
+        <v>128458375</v>
       </c>
       <c r="B65" t="n">
-        <v>80194</v>
+        <v>80257</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679446</v>
+        <v>679437</v>
       </c>
       <c r="R65" t="n">
-        <v>7118101</v>
+        <v>7117961</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458375</v>
+        <v>128458680</v>
       </c>
       <c r="B66" t="n">
-        <v>80230</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679437</v>
+        <v>679472</v>
       </c>
       <c r="R66" t="n">
-        <v>7117961</v>
+        <v>7118058</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7540,7 +7540,7 @@
         <v>128458353</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,10 +7639,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458674</v>
+        <v>128458672</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679408</v>
+        <v>679298</v>
       </c>
       <c r="R68" t="n">
-        <v>7117925</v>
+        <v>7118058</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128458382</v>
+        <v>128458370</v>
       </c>
       <c r="B69" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7747,21 +7747,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>679440</v>
+        <v>679433</v>
       </c>
       <c r="R69" t="n">
-        <v>7117885</v>
+        <v>7117926</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7809,18 +7809,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7839,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458672</v>
+        <v>128458664</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,21 +7844,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7874,10 +7868,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679298</v>
+        <v>679459</v>
       </c>
       <c r="R70" t="n">
-        <v>7118058</v>
+        <v>7118087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7936,10 +7930,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458681</v>
+        <v>128458674</v>
       </c>
       <c r="B71" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7971,10 +7965,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679506</v>
+        <v>679408</v>
       </c>
       <c r="R71" t="n">
-        <v>7118062</v>
+        <v>7117925</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8033,10 +8027,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458370</v>
+        <v>128458382</v>
       </c>
       <c r="B72" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8044,21 +8038,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8068,10 +8062,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679433</v>
+        <v>679440</v>
       </c>
       <c r="R72" t="n">
-        <v>7117926</v>
+        <v>7117885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8106,12 +8100,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458664</v>
+        <v>128458681</v>
       </c>
       <c r="B73" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8141,21 +8141,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679459</v>
+        <v>679506</v>
       </c>
       <c r="R73" t="n">
-        <v>7118087</v>
+        <v>7118062</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>128458389</v>
       </c>
       <c r="B75" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>128458642</v>
       </c>
       <c r="B76" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458675</v>
+        <v>128458349</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>80250</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679390</v>
+        <v>679455</v>
       </c>
       <c r="R77" t="n">
-        <v>7118002</v>
+        <v>7117858</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,10 +8615,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458349</v>
+        <v>128458641</v>
       </c>
       <c r="B78" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679455</v>
+        <v>679393</v>
       </c>
       <c r="R78" t="n">
-        <v>7117858</v>
+        <v>7118025</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458641</v>
+        <v>128458675</v>
       </c>
       <c r="B79" t="n">
-        <v>80223</v>
+        <v>79116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679393</v>
+        <v>679390</v>
       </c>
       <c r="R79" t="n">
-        <v>7118025</v>
+        <v>7118002</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458645</v>
+        <v>128458638</v>
       </c>
       <c r="B80" t="n">
-        <v>57686</v>
+        <v>79148</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679307</v>
+        <v>679347</v>
       </c>
       <c r="R80" t="n">
-        <v>7117932</v>
+        <v>7117856</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,6 +8888,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8906,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>79121</v>
+        <v>57713</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8918,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R81" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,7 +8986,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458381</v>
+        <v>128458356</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679414</v>
+        <v>679480</v>
       </c>
       <c r="R27" t="n">
-        <v>7117929</v>
+        <v>7117930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,7 +3698,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3717,7 +3716,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458673</v>
+        <v>128458381</v>
       </c>
       <c r="B28" t="n">
         <v>79116</v>
@@ -3752,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679328</v>
+        <v>679414</v>
       </c>
       <c r="R28" t="n">
-        <v>7117932</v>
+        <v>7117929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,12 +3789,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3814,10 +3819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458365</v>
+        <v>128458673</v>
       </c>
       <c r="B29" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3825,21 +3830,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,10 +3854,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679464</v>
+        <v>679328</v>
       </c>
       <c r="R29" t="n">
-        <v>7117976</v>
+        <v>7117932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3893,7 +3898,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3912,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458356</v>
+        <v>128458365</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,21 +3927,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3947,10 +3951,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679480</v>
+        <v>679464</v>
       </c>
       <c r="R30" t="n">
-        <v>7117930</v>
+        <v>7117976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,17 +3989,13 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458386</v>
+        <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679411</v>
+        <v>679409</v>
       </c>
       <c r="R36" t="n">
-        <v>7117970</v>
+        <v>7117952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458372</v>
+        <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679409</v>
+        <v>679411</v>
       </c>
       <c r="R37" t="n">
-        <v>7117952</v>
+        <v>7117970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458677</v>
+        <v>128458640</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>80250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679355</v>
+        <v>679458</v>
       </c>
       <c r="R40" t="n">
-        <v>7118031</v>
+        <v>7118097</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4984,32 +4984,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458640</v>
+        <v>128458364</v>
       </c>
       <c r="B41" t="n">
-        <v>80250</v>
+        <v>80221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679458</v>
+        <v>679421</v>
       </c>
       <c r="R41" t="n">
-        <v>7118097</v>
+        <v>7117929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5063,6 +5063,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5081,10 +5082,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458364</v>
+        <v>128458677</v>
       </c>
       <c r="B42" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,21 +5093,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5116,10 +5117,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679421</v>
+        <v>679355</v>
       </c>
       <c r="R42" t="n">
-        <v>7117929</v>
+        <v>7118031</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5160,7 +5161,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458661</v>
+        <v>128458384</v>
       </c>
       <c r="B45" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679395</v>
+        <v>679443</v>
       </c>
       <c r="R45" t="n">
-        <v>7117956</v>
+        <v>7117919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,12 +5446,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5470,7 +5476,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458371</v>
+        <v>128458661</v>
       </c>
       <c r="B46" t="n">
         <v>80221</v>
@@ -5505,10 +5511,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679394</v>
+        <v>679395</v>
       </c>
       <c r="R46" t="n">
-        <v>7117935</v>
+        <v>7117956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5567,10 +5573,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458384</v>
+        <v>128458371</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5578,21 +5584,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5608,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679443</v>
+        <v>679394</v>
       </c>
       <c r="R47" t="n">
-        <v>7117919</v>
+        <v>7117935</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5640,18 +5646,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458692</v>
+        <v>128458342</v>
       </c>
       <c r="B48" t="n">
-        <v>88894</v>
+        <v>56907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679349</v>
+        <v>679446</v>
       </c>
       <c r="R48" t="n">
-        <v>7117913</v>
+        <v>7117918</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,32 +5767,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458342</v>
+        <v>128458662</v>
       </c>
       <c r="B49" t="n">
-        <v>56907</v>
+        <v>80221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679446</v>
+        <v>679403</v>
       </c>
       <c r="R49" t="n">
-        <v>7117918</v>
+        <v>7117960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458388</v>
+        <v>128458373</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679456</v>
+        <v>679404</v>
       </c>
       <c r="R50" t="n">
-        <v>7118056</v>
+        <v>7117977</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458662</v>
+        <v>128458388</v>
       </c>
       <c r="B51" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679403</v>
+        <v>679456</v>
       </c>
       <c r="R51" t="n">
-        <v>7117960</v>
+        <v>7118056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458373</v>
+        <v>128458692</v>
       </c>
       <c r="B52" t="n">
-        <v>80221</v>
+        <v>88894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679404</v>
+        <v>679349</v>
       </c>
       <c r="R52" t="n">
-        <v>7117977</v>
+        <v>7117913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458368</v>
+        <v>128458351</v>
       </c>
       <c r="B55" t="n">
-        <v>80221</v>
+        <v>80250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679446</v>
+        <v>679464</v>
       </c>
       <c r="R55" t="n">
-        <v>7117937</v>
+        <v>7117976</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458351</v>
+        <v>128458368</v>
       </c>
       <c r="B56" t="n">
-        <v>80250</v>
+        <v>80221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679464</v>
+        <v>679446</v>
       </c>
       <c r="R56" t="n">
-        <v>7117976</v>
+        <v>7117937</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458350</v>
+        <v>128458358</v>
       </c>
       <c r="B57" t="n">
-        <v>80250</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679446</v>
+        <v>679474</v>
       </c>
       <c r="R57" t="n">
-        <v>7117860</v>
+        <v>7117950</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,6 +6614,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6640,32 +6645,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>80250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6675,10 +6680,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R58" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6711,11 +6716,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7149,7 +7149,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458366</v>
+        <v>128458663</v>
       </c>
       <c r="B63" t="n">
         <v>80221</v>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679455</v>
+        <v>679446</v>
       </c>
       <c r="R63" t="n">
-        <v>7117858</v>
+        <v>7118101</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458663</v>
+        <v>128458375</v>
       </c>
       <c r="B64" t="n">
-        <v>80221</v>
+        <v>80257</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679446</v>
+        <v>679437</v>
       </c>
       <c r="R64" t="n">
-        <v>7118101</v>
+        <v>7117961</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458375</v>
+        <v>128458353</v>
       </c>
       <c r="B65" t="n">
-        <v>80257</v>
+        <v>57716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679437</v>
+        <v>679512</v>
       </c>
       <c r="R65" t="n">
-        <v>7117961</v>
+        <v>7118001</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7414,6 +7414,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7537,10 +7542,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458353</v>
+        <v>128458366</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7548,21 +7553,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7572,10 +7577,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679512</v>
+        <v>679455</v>
       </c>
       <c r="R67" t="n">
-        <v>7118001</v>
+        <v>7117858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7608,11 +7613,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7639,10 +7639,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458672</v>
+        <v>128458370</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7650,21 +7650,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679298</v>
+        <v>679433</v>
       </c>
       <c r="R68" t="n">
-        <v>7118058</v>
+        <v>7117926</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128458370</v>
+        <v>128458674</v>
       </c>
       <c r="B69" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7747,21 +7747,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>679433</v>
+        <v>679408</v>
       </c>
       <c r="R69" t="n">
-        <v>7117926</v>
+        <v>7117925</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7833,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458664</v>
+        <v>128458382</v>
       </c>
       <c r="B70" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7844,21 +7844,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679459</v>
+        <v>679440</v>
       </c>
       <c r="R70" t="n">
-        <v>7118087</v>
+        <v>7117885</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7906,12 +7906,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7930,7 +7936,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458674</v>
+        <v>128458672</v>
       </c>
       <c r="B71" t="n">
         <v>79116</v>
@@ -7965,10 +7971,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679408</v>
+        <v>679298</v>
       </c>
       <c r="R71" t="n">
-        <v>7117925</v>
+        <v>7118058</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8027,7 +8033,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458382</v>
+        <v>128458681</v>
       </c>
       <c r="B72" t="n">
         <v>79116</v>
@@ -8062,10 +8068,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679440</v>
+        <v>679506</v>
       </c>
       <c r="R72" t="n">
-        <v>7117885</v>
+        <v>7118062</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8100,18 +8106,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458681</v>
+        <v>128458664</v>
       </c>
       <c r="B73" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8141,21 +8141,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679506</v>
+        <v>679459</v>
       </c>
       <c r="R73" t="n">
-        <v>7118062</v>
+        <v>7118087</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458385</v>
+        <v>128458657</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679315</v>
+        <v>679407</v>
       </c>
       <c r="R23" t="n">
-        <v>7118058</v>
+        <v>7117906</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,6 +3282,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3311,7 +3316,7 @@
         <v>128458658</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458657</v>
+        <v>128458385</v>
       </c>
       <c r="B25" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,21 +3426,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3445,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679407</v>
+        <v>679315</v>
       </c>
       <c r="R25" t="n">
-        <v>7117906</v>
+        <v>7118058</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,11 +3486,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458356</v>
+        <v>128458365</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679480</v>
+        <v>679464</v>
       </c>
       <c r="R27" t="n">
-        <v>7117930</v>
+        <v>7117976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3687,17 +3687,13 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3716,10 +3712,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458381</v>
+        <v>128458673</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,10 +3747,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679414</v>
+        <v>679328</v>
       </c>
       <c r="R28" t="n">
-        <v>7117929</v>
+        <v>7117932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3789,18 +3785,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3819,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458673</v>
+        <v>128458381</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,10 +3844,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679328</v>
+        <v>679414</v>
       </c>
       <c r="R29" t="n">
-        <v>7117932</v>
+        <v>7117929</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3892,12 +3882,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3916,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458365</v>
+        <v>128458356</v>
       </c>
       <c r="B30" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,21 +3923,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3951,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679464</v>
+        <v>679480</v>
       </c>
       <c r="R30" t="n">
-        <v>7117976</v>
+        <v>7117930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3989,13 +3985,17 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4111,27 +4111,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458399</v>
+        <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>80256</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679418</v>
+        <v>679402</v>
       </c>
       <c r="R32" t="n">
-        <v>7117932</v>
+        <v>7117958</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4208,27 +4208,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458670</v>
+        <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>80260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679402</v>
+        <v>679418</v>
       </c>
       <c r="R33" t="n">
-        <v>7117958</v>
+        <v>7117932</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
         <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>91505</v>
+        <v>91515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458372</v>
+        <v>128458369</v>
       </c>
       <c r="B36" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679409</v>
+        <v>679437</v>
       </c>
       <c r="R36" t="n">
-        <v>7117952</v>
+        <v>7117961</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4599,7 +4599,7 @@
         <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458369</v>
+        <v>128458659</v>
       </c>
       <c r="B38" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679437</v>
+        <v>679419</v>
       </c>
       <c r="R38" t="n">
-        <v>7117961</v>
+        <v>7118102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458659</v>
+        <v>128458372</v>
       </c>
       <c r="B39" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679419</v>
+        <v>679409</v>
       </c>
       <c r="R39" t="n">
-        <v>7118102</v>
+        <v>7117952</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458640</v>
+        <v>128458677</v>
       </c>
       <c r="B40" t="n">
-        <v>80250</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679458</v>
+        <v>679355</v>
       </c>
       <c r="R40" t="n">
-        <v>7118097</v>
+        <v>7118031</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458364</v>
+        <v>128458660</v>
       </c>
       <c r="B41" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679421</v>
+        <v>679372</v>
       </c>
       <c r="R41" t="n">
-        <v>7117929</v>
+        <v>7117955</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5063,7 +5063,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5082,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458677</v>
+        <v>128458364</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,21 +5092,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5117,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679355</v>
+        <v>679421</v>
       </c>
       <c r="R42" t="n">
-        <v>7118031</v>
+        <v>7117929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5161,6 +5160,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5179,32 +5179,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458660</v>
+        <v>128458640</v>
       </c>
       <c r="B43" t="n">
-        <v>80221</v>
+        <v>80254</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679372</v>
+        <v>679458</v>
       </c>
       <c r="R43" t="n">
-        <v>7117955</v>
+        <v>7118097</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458340</v>
+        <v>128458371</v>
       </c>
       <c r="B44" t="n">
-        <v>79735</v>
+        <v>80225</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679488</v>
+        <v>679394</v>
       </c>
       <c r="R44" t="n">
-        <v>7118028</v>
+        <v>7117935</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458384</v>
+        <v>128458340</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679443</v>
+        <v>679488</v>
       </c>
       <c r="R45" t="n">
-        <v>7117919</v>
+        <v>7118028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,18 +5446,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5476,10 +5470,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458661</v>
+        <v>128458384</v>
       </c>
       <c r="B46" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5487,21 +5481,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5511,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679395</v>
+        <v>679443</v>
       </c>
       <c r="R46" t="n">
-        <v>7117956</v>
+        <v>7117919</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,12 +5543,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5573,10 +5573,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458371</v>
+        <v>128458661</v>
       </c>
       <c r="B47" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679394</v>
+        <v>679395</v>
       </c>
       <c r="R47" t="n">
-        <v>7117935</v>
+        <v>7117956</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458342</v>
+        <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>56907</v>
+        <v>88904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679446</v>
+        <v>679349</v>
       </c>
       <c r="R48" t="n">
-        <v>7117918</v>
+        <v>7117913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458662</v>
+        <v>128458388</v>
       </c>
       <c r="B49" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679403</v>
+        <v>679456</v>
       </c>
       <c r="R49" t="n">
-        <v>7117960</v>
+        <v>7118056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458373</v>
+        <v>128458374</v>
       </c>
       <c r="B50" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679404</v>
+        <v>679493</v>
       </c>
       <c r="R50" t="n">
-        <v>7117977</v>
+        <v>7118012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458388</v>
+        <v>128458373</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679456</v>
+        <v>679404</v>
       </c>
       <c r="R51" t="n">
-        <v>7118056</v>
+        <v>7117977</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B52" t="n">
-        <v>88894</v>
+        <v>80225</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R52" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458374</v>
+        <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>80221</v>
+        <v>56907</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679493</v>
+        <v>679446</v>
       </c>
       <c r="R53" t="n">
-        <v>7118012</v>
+        <v>7117918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,7 +6255,7 @@
         <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458351</v>
+        <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80250</v>
+        <v>80225</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679464</v>
+        <v>679446</v>
       </c>
       <c r="R55" t="n">
-        <v>7117976</v>
+        <v>7117937</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458368</v>
+        <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80221</v>
+        <v>80254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679446</v>
+        <v>679464</v>
       </c>
       <c r="R56" t="n">
-        <v>7117937</v>
+        <v>7117976</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>80254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R57" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,11 +6614,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6645,32 +6640,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458350</v>
+        <v>128458358</v>
       </c>
       <c r="B58" t="n">
-        <v>80250</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6680,10 +6675,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679446</v>
+        <v>679474</v>
       </c>
       <c r="R58" t="n">
-        <v>7117860</v>
+        <v>7117950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6716,6 +6711,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6745,7 +6745,7 @@
         <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6839,32 +6839,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>58086</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R60" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B61" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R61" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458663</v>
+        <v>128458680</v>
       </c>
       <c r="B63" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679446</v>
+        <v>679472</v>
       </c>
       <c r="R63" t="n">
-        <v>7118101</v>
+        <v>7118058</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7249,7 +7249,7 @@
         <v>128458375</v>
       </c>
       <c r="B64" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458353</v>
+        <v>128458663</v>
       </c>
       <c r="B65" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7354,21 +7354,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679512</v>
+        <v>679446</v>
       </c>
       <c r="R65" t="n">
-        <v>7118001</v>
+        <v>7118101</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7414,11 +7414,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7445,10 +7440,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458680</v>
+        <v>128458366</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7456,21 +7451,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7480,10 +7475,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679472</v>
+        <v>679455</v>
       </c>
       <c r="R66" t="n">
-        <v>7118058</v>
+        <v>7117858</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7542,10 +7537,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458366</v>
+        <v>128458353</v>
       </c>
       <c r="B67" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7553,21 +7548,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7577,10 +7572,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679455</v>
+        <v>679512</v>
       </c>
       <c r="R67" t="n">
-        <v>7117858</v>
+        <v>7118001</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7613,6 +7608,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7639,10 +7639,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458370</v>
+        <v>128458681</v>
       </c>
       <c r="B68" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7650,21 +7650,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679433</v>
+        <v>679506</v>
       </c>
       <c r="R68" t="n">
-        <v>7117926</v>
+        <v>7118062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7739,7 +7739,7 @@
         <v>128458674</v>
       </c>
       <c r="B69" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7833,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458382</v>
+        <v>128458664</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7844,21 +7844,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679440</v>
+        <v>679459</v>
       </c>
       <c r="R70" t="n">
-        <v>7117885</v>
+        <v>7118087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7906,18 +7906,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7936,10 +7930,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458672</v>
+        <v>128458370</v>
       </c>
       <c r="B71" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7947,21 +7941,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7971,10 +7965,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679298</v>
+        <v>679433</v>
       </c>
       <c r="R71" t="n">
-        <v>7118058</v>
+        <v>7117926</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8033,10 +8027,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458681</v>
+        <v>128458672</v>
       </c>
       <c r="B72" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8068,10 +8062,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679506</v>
+        <v>679298</v>
       </c>
       <c r="R72" t="n">
-        <v>7118062</v>
+        <v>7118058</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8130,10 +8124,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458664</v>
+        <v>128458382</v>
       </c>
       <c r="B73" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8141,21 +8135,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8165,10 +8159,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679459</v>
+        <v>679440</v>
       </c>
       <c r="R73" t="n">
-        <v>7118087</v>
+        <v>7117885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8203,12 +8197,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8227,10 +8227,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458671</v>
+        <v>128458389</v>
       </c>
       <c r="B74" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679436</v>
+        <v>679512</v>
       </c>
       <c r="R74" t="n">
-        <v>7118086</v>
+        <v>7118001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,32 +8324,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458389</v>
+        <v>128458642</v>
       </c>
       <c r="B75" t="n">
-        <v>79116</v>
+        <v>80254</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679512</v>
+        <v>679445</v>
       </c>
       <c r="R75" t="n">
-        <v>7118001</v>
+        <v>7118102</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458642</v>
+        <v>128458671</v>
       </c>
       <c r="B76" t="n">
-        <v>80250</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679445</v>
+        <v>679436</v>
       </c>
       <c r="R76" t="n">
-        <v>7118102</v>
+        <v>7118086</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8521,7 +8521,7 @@
         <v>128458349</v>
       </c>
       <c r="B77" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128458641</v>
       </c>
       <c r="B78" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128458675</v>
       </c>
       <c r="B79" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8809,32 +8809,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458638</v>
+        <v>128458377</v>
       </c>
       <c r="B80" t="n">
-        <v>79148</v>
+        <v>58086</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679347</v>
+        <v>679279</v>
       </c>
       <c r="R80" t="n">
-        <v>7117856</v>
+        <v>7118000</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,7 +8888,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8907,10 +8906,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458645</v>
+        <v>128458638</v>
       </c>
       <c r="B81" t="n">
-        <v>57713</v>
+        <v>79152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8918,21 +8917,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8942,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679307</v>
+        <v>679347</v>
       </c>
       <c r="R81" t="n">
-        <v>7117932</v>
+        <v>7117856</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8986,6 +8985,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,27 +9004,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458377</v>
+        <v>128458645</v>
       </c>
       <c r="B82" t="n">
-        <v>58086</v>
+        <v>57713</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679279</v>
+        <v>679307</v>
       </c>
       <c r="R82" t="n">
-        <v>7118000</v>
+        <v>7117932</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458657</v>
+        <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679407</v>
+        <v>679315</v>
       </c>
       <c r="R23" t="n">
-        <v>7117906</v>
+        <v>7118058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,11 +3282,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3415,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458385</v>
+        <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,21 +3421,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3445,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679315</v>
+        <v>679407</v>
       </c>
       <c r="R25" t="n">
-        <v>7118058</v>
+        <v>7117906</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3486,6 +3481,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458365</v>
+        <v>128458381</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679464</v>
+        <v>679414</v>
       </c>
       <c r="R27" t="n">
-        <v>7117976</v>
+        <v>7117929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3685,6 +3685,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3809,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458381</v>
+        <v>128458356</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3844,10 +3849,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679414</v>
+        <v>679480</v>
       </c>
       <c r="R29" t="n">
-        <v>7117929</v>
+        <v>7117930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3884,7 +3889,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,7 +3898,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3912,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458356</v>
+        <v>128458365</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,21 +3927,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3947,10 +3951,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679480</v>
+        <v>679464</v>
       </c>
       <c r="R30" t="n">
-        <v>7117930</v>
+        <v>7117976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,17 +3989,13 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458644</v>
+        <v>128458679</v>
       </c>
       <c r="B34" t="n">
-        <v>91515</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679456</v>
+        <v>679434</v>
       </c>
       <c r="R34" t="n">
-        <v>7118095</v>
+        <v>7118112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458679</v>
+        <v>128458386</v>
       </c>
       <c r="B35" t="n">
         <v>79120</v>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679434</v>
+        <v>679411</v>
       </c>
       <c r="R35" t="n">
-        <v>7118112</v>
+        <v>7117970</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458369</v>
+        <v>128458372</v>
       </c>
       <c r="B36" t="n">
         <v>80225</v>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679437</v>
+        <v>679409</v>
       </c>
       <c r="R36" t="n">
-        <v>7117961</v>
+        <v>7117952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458386</v>
+        <v>128458369</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679411</v>
+        <v>679437</v>
       </c>
       <c r="R37" t="n">
-        <v>7117970</v>
+        <v>7117961</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458372</v>
+        <v>128458644</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>91515</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679409</v>
+        <v>679456</v>
       </c>
       <c r="R39" t="n">
-        <v>7117952</v>
+        <v>7118095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4984,32 +4984,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458660</v>
+        <v>128458640</v>
       </c>
       <c r="B41" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679372</v>
+        <v>679458</v>
       </c>
       <c r="R41" t="n">
-        <v>7117955</v>
+        <v>7118097</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5179,32 +5179,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458640</v>
+        <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80254</v>
+        <v>80225</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679458</v>
+        <v>679372</v>
       </c>
       <c r="R43" t="n">
-        <v>7118097</v>
+        <v>7117955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458371</v>
+        <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>80225</v>
+        <v>79739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679394</v>
+        <v>679488</v>
       </c>
       <c r="R44" t="n">
-        <v>7117935</v>
+        <v>7118028</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458340</v>
+        <v>128458661</v>
       </c>
       <c r="B45" t="n">
-        <v>79739</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679488</v>
+        <v>679395</v>
       </c>
       <c r="R45" t="n">
-        <v>7118028</v>
+        <v>7117956</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458384</v>
+        <v>128458371</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679443</v>
+        <v>679394</v>
       </c>
       <c r="R46" t="n">
-        <v>7117919</v>
+        <v>7117935</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5543,18 +5543,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5573,10 +5567,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458661</v>
+        <v>128458384</v>
       </c>
       <c r="B47" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5584,21 +5578,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5608,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679395</v>
+        <v>679443</v>
       </c>
       <c r="R47" t="n">
-        <v>7117956</v>
+        <v>7117919</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,12 +5640,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B48" t="n">
-        <v>88904</v>
+        <v>80225</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R48" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458388</v>
+        <v>128458374</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679456</v>
+        <v>679493</v>
       </c>
       <c r="R49" t="n">
-        <v>7118056</v>
+        <v>7118012</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458374</v>
+        <v>128458692</v>
       </c>
       <c r="B50" t="n">
-        <v>80225</v>
+        <v>88904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679493</v>
+        <v>679349</v>
       </c>
       <c r="R50" t="n">
-        <v>7118012</v>
+        <v>7117913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458373</v>
+        <v>128458388</v>
       </c>
       <c r="B51" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679404</v>
+        <v>679456</v>
       </c>
       <c r="R51" t="n">
-        <v>7117977</v>
+        <v>7118056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458662</v>
+        <v>128458342</v>
       </c>
       <c r="B52" t="n">
-        <v>80225</v>
+        <v>56907</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679403</v>
+        <v>679446</v>
       </c>
       <c r="R52" t="n">
-        <v>7117960</v>
+        <v>7117918</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458342</v>
+        <v>128458373</v>
       </c>
       <c r="B53" t="n">
-        <v>56907</v>
+        <v>80225</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679446</v>
+        <v>679404</v>
       </c>
       <c r="R53" t="n">
-        <v>7117918</v>
+        <v>7117977</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128458643</v>
+        <v>128458351</v>
       </c>
       <c r="B54" t="n">
         <v>80254</v>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679460</v>
+        <v>679464</v>
       </c>
       <c r="R54" t="n">
-        <v>7118089</v>
+        <v>7117976</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458368</v>
+        <v>128458643</v>
       </c>
       <c r="B55" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679446</v>
+        <v>679460</v>
       </c>
       <c r="R55" t="n">
-        <v>7117937</v>
+        <v>7118089</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458351</v>
+        <v>128458368</v>
       </c>
       <c r="B56" t="n">
-        <v>80254</v>
+        <v>80225</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679464</v>
+        <v>679446</v>
       </c>
       <c r="R56" t="n">
-        <v>7117976</v>
+        <v>7117937</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6839,32 +6839,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>58086</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R61" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458375</v>
+        <v>128458353</v>
       </c>
       <c r="B64" t="n">
-        <v>80261</v>
+        <v>57716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679437</v>
+        <v>679512</v>
       </c>
       <c r="R64" t="n">
-        <v>7117961</v>
+        <v>7118001</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7317,6 +7317,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7343,7 +7348,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458663</v>
+        <v>128458366</v>
       </c>
       <c r="B65" t="n">
         <v>80225</v>
@@ -7378,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679446</v>
+        <v>679455</v>
       </c>
       <c r="R65" t="n">
-        <v>7118101</v>
+        <v>7117858</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,7 +7445,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458366</v>
+        <v>128458663</v>
       </c>
       <c r="B66" t="n">
         <v>80225</v>
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679455</v>
+        <v>679446</v>
       </c>
       <c r="R66" t="n">
-        <v>7117858</v>
+        <v>7118101</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7537,32 +7542,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458353</v>
+        <v>128458375</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>80261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7572,10 +7577,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679512</v>
+        <v>679437</v>
       </c>
       <c r="R67" t="n">
-        <v>7118001</v>
+        <v>7117961</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7608,11 +7613,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7639,7 +7639,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458681</v>
+        <v>128458674</v>
       </c>
       <c r="B68" t="n">
         <v>79120</v>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679506</v>
+        <v>679408</v>
       </c>
       <c r="R68" t="n">
-        <v>7118062</v>
+        <v>7117925</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,7 +7736,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128458674</v>
+        <v>128458382</v>
       </c>
       <c r="B69" t="n">
         <v>79120</v>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>679408</v>
+        <v>679440</v>
       </c>
       <c r="R69" t="n">
-        <v>7117925</v>
+        <v>7117885</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7809,12 +7809,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7833,10 +7839,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458664</v>
+        <v>128458672</v>
       </c>
       <c r="B70" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7844,21 +7850,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7868,10 +7874,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679459</v>
+        <v>679298</v>
       </c>
       <c r="R70" t="n">
-        <v>7118087</v>
+        <v>7118058</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7930,10 +7936,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458370</v>
+        <v>128458681</v>
       </c>
       <c r="B71" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7941,21 +7947,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7965,10 +7971,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679433</v>
+        <v>679506</v>
       </c>
       <c r="R71" t="n">
-        <v>7117926</v>
+        <v>7118062</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8027,10 +8033,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458672</v>
+        <v>128458370</v>
       </c>
       <c r="B72" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8038,21 +8044,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8062,10 +8068,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679298</v>
+        <v>679433</v>
       </c>
       <c r="R72" t="n">
-        <v>7118058</v>
+        <v>7117926</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8124,10 +8130,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458382</v>
+        <v>128458664</v>
       </c>
       <c r="B73" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8135,21 +8141,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8159,10 +8165,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679440</v>
+        <v>679459</v>
       </c>
       <c r="R73" t="n">
-        <v>7117885</v>
+        <v>7118087</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8197,18 +8203,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458389</v>
+        <v>128458671</v>
       </c>
       <c r="B74" t="n">
         <v>79120</v>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679512</v>
+        <v>679436</v>
       </c>
       <c r="R74" t="n">
-        <v>7118001</v>
+        <v>7118086</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,32 +8324,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458642</v>
+        <v>128458389</v>
       </c>
       <c r="B75" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679445</v>
+        <v>679512</v>
       </c>
       <c r="R75" t="n">
-        <v>7118102</v>
+        <v>7118001</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458671</v>
+        <v>128458642</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679436</v>
+        <v>679445</v>
       </c>
       <c r="R76" t="n">
-        <v>7118086</v>
+        <v>7118102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458349</v>
+        <v>128458675</v>
       </c>
       <c r="B77" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679455</v>
+        <v>679390</v>
       </c>
       <c r="R77" t="n">
-        <v>7117858</v>
+        <v>7118002</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,7 +8615,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458641</v>
+        <v>128458349</v>
       </c>
       <c r="B78" t="n">
         <v>80254</v>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679393</v>
+        <v>679455</v>
       </c>
       <c r="R78" t="n">
-        <v>7118025</v>
+        <v>7117858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458675</v>
+        <v>128458641</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679390</v>
+        <v>679393</v>
       </c>
       <c r="R79" t="n">
-        <v>7118002</v>
+        <v>7118025</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8809,32 +8809,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B80" t="n">
-        <v>58086</v>
+        <v>79152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R80" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,6 +8888,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8906,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>79152</v>
+        <v>57713</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,21 +8918,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8941,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R81" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,7 +8986,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,27 +9004,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>57713</v>
+        <v>58086</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R82" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458385</v>
+        <v>128458658</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679315</v>
+        <v>679386</v>
       </c>
       <c r="R23" t="n">
-        <v>7118058</v>
+        <v>7118036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,6 +3282,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3308,7 +3313,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458658</v>
+        <v>128458657</v>
       </c>
       <c r="B24" t="n">
         <v>80225</v>
@@ -3343,10 +3348,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679386</v>
+        <v>679407</v>
       </c>
       <c r="R24" t="n">
-        <v>7118036</v>
+        <v>7117906</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3383,7 +3388,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458657</v>
+        <v>128458385</v>
       </c>
       <c r="B25" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,21 +3426,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3445,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679407</v>
+        <v>679315</v>
       </c>
       <c r="R25" t="n">
-        <v>7117906</v>
+        <v>7118058</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,11 +3486,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458381</v>
+        <v>128458356</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679414</v>
+        <v>679480</v>
       </c>
       <c r="R27" t="n">
-        <v>7117929</v>
+        <v>7117930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,7 +3698,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3717,7 +3716,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458673</v>
+        <v>128458381</v>
       </c>
       <c r="B28" t="n">
         <v>79120</v>
@@ -3752,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679328</v>
+        <v>679414</v>
       </c>
       <c r="R28" t="n">
-        <v>7117932</v>
+        <v>7117929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,12 +3789,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3814,10 +3819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458356</v>
+        <v>128458673</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3825,21 +3830,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,10 +3854,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679480</v>
+        <v>679328</v>
       </c>
       <c r="R29" t="n">
-        <v>7117930</v>
+        <v>7117932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3885,11 +3890,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458679</v>
+        <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>91515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679434</v>
+        <v>679456</v>
       </c>
       <c r="R34" t="n">
-        <v>7118112</v>
+        <v>7118095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458386</v>
+        <v>128458659</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679411</v>
+        <v>679419</v>
       </c>
       <c r="R35" t="n">
-        <v>7117970</v>
+        <v>7118102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458372</v>
+        <v>128458679</v>
       </c>
       <c r="B36" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679409</v>
+        <v>679434</v>
       </c>
       <c r="R36" t="n">
-        <v>7117952</v>
+        <v>7118112</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458369</v>
+        <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679437</v>
+        <v>679411</v>
       </c>
       <c r="R37" t="n">
-        <v>7117961</v>
+        <v>7117970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458659</v>
+        <v>128458372</v>
       </c>
       <c r="B38" t="n">
         <v>80225</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679419</v>
+        <v>679409</v>
       </c>
       <c r="R38" t="n">
-        <v>7118102</v>
+        <v>7117952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458644</v>
+        <v>128458369</v>
       </c>
       <c r="B39" t="n">
-        <v>91515</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679456</v>
+        <v>679437</v>
       </c>
       <c r="R39" t="n">
-        <v>7118095</v>
+        <v>7117961</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458658</v>
+        <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679386</v>
+        <v>679315</v>
       </c>
       <c r="R23" t="n">
-        <v>7118036</v>
+        <v>7118058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,11 +3282,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3313,7 +3308,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458657</v>
+        <v>128458658</v>
       </c>
       <c r="B24" t="n">
         <v>80225</v>
@@ -3348,10 +3343,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679407</v>
+        <v>679386</v>
       </c>
       <c r="R24" t="n">
-        <v>7117906</v>
+        <v>7118036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3388,7 +3383,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>björk</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458385</v>
+        <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,21 +3421,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3445,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679315</v>
+        <v>679407</v>
       </c>
       <c r="R25" t="n">
-        <v>7118058</v>
+        <v>7117906</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3486,6 +3481,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458356</v>
+        <v>128458365</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679480</v>
+        <v>679464</v>
       </c>
       <c r="R27" t="n">
-        <v>7117930</v>
+        <v>7117976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3687,17 +3687,13 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3916,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458365</v>
+        <v>128458356</v>
       </c>
       <c r="B30" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,21 +3923,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3951,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679464</v>
+        <v>679480</v>
       </c>
       <c r="R30" t="n">
-        <v>7117976</v>
+        <v>7117930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3989,13 +3985,17 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458644</v>
+        <v>128458372</v>
       </c>
       <c r="B34" t="n">
-        <v>91515</v>
+        <v>80225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679456</v>
+        <v>679409</v>
       </c>
       <c r="R34" t="n">
-        <v>7118095</v>
+        <v>7117952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458659</v>
+        <v>128458369</v>
       </c>
       <c r="B35" t="n">
         <v>80225</v>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679419</v>
+        <v>679437</v>
       </c>
       <c r="R35" t="n">
-        <v>7118102</v>
+        <v>7117961</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458679</v>
+        <v>128458659</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679434</v>
+        <v>679419</v>
       </c>
       <c r="R36" t="n">
-        <v>7118112</v>
+        <v>7118102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458386</v>
+        <v>128458679</v>
       </c>
       <c r="B37" t="n">
         <v>79120</v>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679411</v>
+        <v>679434</v>
       </c>
       <c r="R37" t="n">
-        <v>7117970</v>
+        <v>7118112</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,32 +4693,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458372</v>
+        <v>128458644</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>91515</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679409</v>
+        <v>679456</v>
       </c>
       <c r="R38" t="n">
-        <v>7117952</v>
+        <v>7118095</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458369</v>
+        <v>128458386</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679437</v>
+        <v>679411</v>
       </c>
       <c r="R39" t="n">
-        <v>7117961</v>
+        <v>7117970</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458677</v>
+        <v>128458364</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679355</v>
+        <v>679421</v>
       </c>
       <c r="R40" t="n">
-        <v>7118031</v>
+        <v>7117929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4966,6 +4966,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5081,7 +5082,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458364</v>
+        <v>128458660</v>
       </c>
       <c r="B42" t="n">
         <v>80225</v>
@@ -5116,10 +5117,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679421</v>
+        <v>679372</v>
       </c>
       <c r="R42" t="n">
-        <v>7117929</v>
+        <v>7117955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5160,7 +5161,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5179,10 +5179,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458660</v>
+        <v>128458677</v>
       </c>
       <c r="B43" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5190,21 +5190,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679372</v>
+        <v>679355</v>
       </c>
       <c r="R43" t="n">
-        <v>7117955</v>
+        <v>7118031</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458662</v>
+        <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>80225</v>
+        <v>88904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679403</v>
+        <v>679349</v>
       </c>
       <c r="R48" t="n">
-        <v>7117960</v>
+        <v>7117913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458374</v>
+        <v>128458388</v>
       </c>
       <c r="B49" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679493</v>
+        <v>679456</v>
       </c>
       <c r="R49" t="n">
-        <v>7118012</v>
+        <v>7118056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458692</v>
+        <v>128458662</v>
       </c>
       <c r="B50" t="n">
-        <v>88904</v>
+        <v>80225</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679349</v>
+        <v>679403</v>
       </c>
       <c r="R50" t="n">
-        <v>7117913</v>
+        <v>7117960</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458388</v>
+        <v>128458374</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679456</v>
+        <v>679493</v>
       </c>
       <c r="R51" t="n">
-        <v>7118056</v>
+        <v>7118012</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458342</v>
+        <v>128458373</v>
       </c>
       <c r="B52" t="n">
-        <v>56907</v>
+        <v>80225</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679446</v>
+        <v>679404</v>
       </c>
       <c r="R52" t="n">
-        <v>7117918</v>
+        <v>7117977</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458373</v>
+        <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>80225</v>
+        <v>56907</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679404</v>
+        <v>679446</v>
       </c>
       <c r="R53" t="n">
-        <v>7117977</v>
+        <v>7117918</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128458351</v>
+        <v>128458643</v>
       </c>
       <c r="B54" t="n">
         <v>80254</v>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679464</v>
+        <v>679460</v>
       </c>
       <c r="R54" t="n">
-        <v>7117976</v>
+        <v>7118089</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458643</v>
+        <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80254</v>
+        <v>80225</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679460</v>
+        <v>679446</v>
       </c>
       <c r="R55" t="n">
-        <v>7118089</v>
+        <v>7117937</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458368</v>
+        <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679446</v>
+        <v>679464</v>
       </c>
       <c r="R56" t="n">
-        <v>7117937</v>
+        <v>7117976</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B59" t="n">
         <v>79120</v>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R59" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458387</v>
+        <v>128458678</v>
       </c>
       <c r="B60" t="n">
         <v>79120</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679461</v>
+        <v>679369</v>
       </c>
       <c r="R60" t="n">
-        <v>7117988</v>
+        <v>7118112</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458680</v>
+        <v>128458353</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679472</v>
+        <v>679512</v>
       </c>
       <c r="R63" t="n">
-        <v>7118058</v>
+        <v>7118001</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7220,6 +7220,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7246,10 +7251,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458353</v>
+        <v>128458366</v>
       </c>
       <c r="B64" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7257,21 +7262,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679512</v>
+        <v>679455</v>
       </c>
       <c r="R64" t="n">
-        <v>7118001</v>
+        <v>7117858</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7317,11 +7322,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7348,7 +7348,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458366</v>
+        <v>128458663</v>
       </c>
       <c r="B65" t="n">
         <v>80225</v>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679455</v>
+        <v>679446</v>
       </c>
       <c r="R65" t="n">
-        <v>7117858</v>
+        <v>7118101</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7445,32 +7445,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458663</v>
+        <v>128458375</v>
       </c>
       <c r="B66" t="n">
-        <v>80225</v>
+        <v>80261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7480,10 +7480,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679446</v>
+        <v>679437</v>
       </c>
       <c r="R66" t="n">
-        <v>7118101</v>
+        <v>7117961</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7542,32 +7542,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458375</v>
+        <v>128458680</v>
       </c>
       <c r="B67" t="n">
-        <v>80261</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679437</v>
+        <v>679472</v>
       </c>
       <c r="R67" t="n">
-        <v>7117961</v>
+        <v>7118058</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8227,32 +8227,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458671</v>
+        <v>128458642</v>
       </c>
       <c r="B74" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679436</v>
+        <v>679445</v>
       </c>
       <c r="R74" t="n">
-        <v>7118086</v>
+        <v>7118102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,7 +8324,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458389</v>
+        <v>128458671</v>
       </c>
       <c r="B75" t="n">
         <v>79120</v>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679512</v>
+        <v>679436</v>
       </c>
       <c r="R75" t="n">
-        <v>7118001</v>
+        <v>7118086</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458642</v>
+        <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679445</v>
+        <v>679512</v>
       </c>
       <c r="R76" t="n">
-        <v>7118102</v>
+        <v>7118001</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458675</v>
+        <v>128458349</v>
       </c>
       <c r="B77" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679390</v>
+        <v>679455</v>
       </c>
       <c r="R77" t="n">
-        <v>7118002</v>
+        <v>7117858</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,7 +8615,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458349</v>
+        <v>128458641</v>
       </c>
       <c r="B78" t="n">
         <v>80254</v>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679455</v>
+        <v>679393</v>
       </c>
       <c r="R78" t="n">
-        <v>7117858</v>
+        <v>7118025</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458641</v>
+        <v>128458675</v>
       </c>
       <c r="B79" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679393</v>
+        <v>679390</v>
       </c>
       <c r="R79" t="n">
-        <v>7118025</v>
+        <v>7118002</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458638</v>
+        <v>128458645</v>
       </c>
       <c r="B80" t="n">
-        <v>79152</v>
+        <v>57713</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679347</v>
+        <v>679307</v>
       </c>
       <c r="R80" t="n">
-        <v>7117856</v>
+        <v>7117932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,7 +8888,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8907,27 +8906,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458645</v>
+        <v>128458377</v>
       </c>
       <c r="B81" t="n">
-        <v>57713</v>
+        <v>58086</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8942,10 +8941,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679307</v>
+        <v>679279</v>
       </c>
       <c r="R81" t="n">
-        <v>7117932</v>
+        <v>7118000</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9004,32 +9003,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458377</v>
+        <v>128458638</v>
       </c>
       <c r="B82" t="n">
-        <v>58086</v>
+        <v>79152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9039,10 +9038,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679279</v>
+        <v>679347</v>
       </c>
       <c r="R82" t="n">
-        <v>7118000</v>
+        <v>7117856</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9083,6 +9082,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458385</v>
+        <v>128458658</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679315</v>
+        <v>679386</v>
       </c>
       <c r="R23" t="n">
-        <v>7118058</v>
+        <v>7118036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,6 +3282,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3308,10 +3313,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458658</v>
+        <v>128458657</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,10 +3348,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679386</v>
+        <v>679407</v>
       </c>
       <c r="R24" t="n">
-        <v>7118036</v>
+        <v>7117906</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3383,7 +3388,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458657</v>
+        <v>128458385</v>
       </c>
       <c r="B25" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,21 +3426,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3445,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679407</v>
+        <v>679315</v>
       </c>
       <c r="R25" t="n">
-        <v>7117906</v>
+        <v>7118058</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,11 +3486,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,7 +3515,7 @@
         <v>128458648</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458365</v>
+        <v>128458381</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679464</v>
+        <v>679414</v>
       </c>
       <c r="R27" t="n">
-        <v>7117976</v>
+        <v>7117929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3685,6 +3685,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3712,10 +3717,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458381</v>
+        <v>128458673</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679414</v>
+        <v>679328</v>
       </c>
       <c r="R28" t="n">
-        <v>7117929</v>
+        <v>7117932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3785,18 +3790,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3815,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458673</v>
+        <v>128458356</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,21 +3825,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3850,10 +3849,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679328</v>
+        <v>679480</v>
       </c>
       <c r="R29" t="n">
-        <v>7117932</v>
+        <v>7117930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3886,6 +3885,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458356</v>
+        <v>128458365</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>80229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,21 +3927,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3947,10 +3951,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679480</v>
+        <v>679464</v>
       </c>
       <c r="R30" t="n">
-        <v>7117930</v>
+        <v>7117976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,17 +3989,13 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>128458344</v>
       </c>
       <c r="B31" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128458372</v>
       </c>
       <c r="B34" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>128458369</v>
       </c>
       <c r="B35" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>128458659</v>
       </c>
       <c r="B36" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,32 +4596,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458679</v>
+        <v>128458644</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>91519</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679434</v>
+        <v>679456</v>
       </c>
       <c r="R37" t="n">
-        <v>7118112</v>
+        <v>7118095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,32 +4693,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458644</v>
+        <v>128458679</v>
       </c>
       <c r="B38" t="n">
-        <v>91515</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679456</v>
+        <v>679434</v>
       </c>
       <c r="R38" t="n">
-        <v>7118095</v>
+        <v>7118112</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
         <v>128458386</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458364</v>
+        <v>128458677</v>
       </c>
       <c r="B40" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679421</v>
+        <v>679355</v>
       </c>
       <c r="R40" t="n">
-        <v>7117929</v>
+        <v>7118031</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4966,7 +4966,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4988,7 +4987,7 @@
         <v>128458640</v>
       </c>
       <c r="B41" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5082,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458660</v>
+        <v>128458364</v>
       </c>
       <c r="B42" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5117,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679372</v>
+        <v>679421</v>
       </c>
       <c r="R42" t="n">
-        <v>7117955</v>
+        <v>7117929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5161,6 +5160,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5179,10 +5179,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458677</v>
+        <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5190,21 +5190,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679355</v>
+        <v>679372</v>
       </c>
       <c r="R43" t="n">
-        <v>7118031</v>
+        <v>7117955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
         <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458661</v>
+        <v>128458384</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679395</v>
+        <v>679443</v>
       </c>
       <c r="R45" t="n">
-        <v>7117956</v>
+        <v>7117919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,12 +5446,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5470,10 +5476,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458371</v>
+        <v>128458661</v>
       </c>
       <c r="B46" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5505,10 +5511,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679394</v>
+        <v>679395</v>
       </c>
       <c r="R46" t="n">
-        <v>7117935</v>
+        <v>7117956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5567,10 +5573,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458384</v>
+        <v>128458371</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5578,21 +5584,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5608,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679443</v>
+        <v>679394</v>
       </c>
       <c r="R47" t="n">
-        <v>7117919</v>
+        <v>7117935</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5640,18 +5646,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>128458692</v>
       </c>
       <c r="B48" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>128458388</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>128458662</v>
       </c>
       <c r="B50" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458374</v>
+        <v>128458373</v>
       </c>
       <c r="B51" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679493</v>
+        <v>679404</v>
       </c>
       <c r="R51" t="n">
-        <v>7118012</v>
+        <v>7117977</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458373</v>
+        <v>128458374</v>
       </c>
       <c r="B52" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679404</v>
+        <v>679493</v>
       </c>
       <c r="R52" t="n">
-        <v>7117977</v>
+        <v>7118012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
         <v>128458342</v>
       </c>
       <c r="B53" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128458643</v>
+        <v>128458351</v>
       </c>
       <c r="B54" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679460</v>
+        <v>679464</v>
       </c>
       <c r="R54" t="n">
-        <v>7118089</v>
+        <v>7117976</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458368</v>
+        <v>128458643</v>
       </c>
       <c r="B55" t="n">
-        <v>80225</v>
+        <v>80258</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679446</v>
+        <v>679460</v>
       </c>
       <c r="R55" t="n">
-        <v>7117937</v>
+        <v>7118089</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458351</v>
+        <v>128458368</v>
       </c>
       <c r="B56" t="n">
-        <v>80254</v>
+        <v>80229</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679464</v>
+        <v>679446</v>
       </c>
       <c r="R56" t="n">
-        <v>7117976</v>
+        <v>7117937</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128458350</v>
+        <v>128458358</v>
       </c>
       <c r="B57" t="n">
-        <v>80254</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679446</v>
+        <v>679474</v>
       </c>
       <c r="R57" t="n">
-        <v>7117860</v>
+        <v>7117950</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,6 +6614,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6640,32 +6645,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128458358</v>
+        <v>128458350</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>80258</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6675,10 +6680,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679474</v>
+        <v>679446</v>
       </c>
       <c r="R58" t="n">
-        <v>7117950</v>
+        <v>7117860</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6711,11 +6716,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,10 +6742,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458387</v>
+        <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679461</v>
+        <v>679369</v>
       </c>
       <c r="R59" t="n">
-        <v>7117988</v>
+        <v>7118112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6939,7 +6939,7 @@
         <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458353</v>
+        <v>128458680</v>
       </c>
       <c r="B63" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679512</v>
+        <v>679472</v>
       </c>
       <c r="R63" t="n">
-        <v>7118001</v>
+        <v>7118058</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7220,11 +7220,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7254,7 +7249,7 @@
         <v>128458366</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,7 +7346,7 @@
         <v>128458663</v>
       </c>
       <c r="B65" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7448,7 +7443,7 @@
         <v>128458375</v>
       </c>
       <c r="B66" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7542,10 +7537,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458680</v>
+        <v>128458353</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7553,21 +7548,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7577,10 +7572,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679472</v>
+        <v>679512</v>
       </c>
       <c r="R67" t="n">
-        <v>7118058</v>
+        <v>7118001</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7613,6 +7608,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7639,10 +7639,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458674</v>
+        <v>128458370</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7650,21 +7650,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679408</v>
+        <v>679433</v>
       </c>
       <c r="R68" t="n">
-        <v>7117925</v>
+        <v>7117926</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128458382</v>
+        <v>128458664</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7747,21 +7747,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>679440</v>
+        <v>679459</v>
       </c>
       <c r="R69" t="n">
-        <v>7117885</v>
+        <v>7118087</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7809,18 +7809,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7839,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458672</v>
+        <v>128458674</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7874,10 +7868,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679298</v>
+        <v>679408</v>
       </c>
       <c r="R70" t="n">
-        <v>7118058</v>
+        <v>7117925</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7936,10 +7930,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458681</v>
+        <v>128458382</v>
       </c>
       <c r="B71" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7971,10 +7965,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679506</v>
+        <v>679440</v>
       </c>
       <c r="R71" t="n">
-        <v>7118062</v>
+        <v>7117885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8009,12 +8003,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8033,10 +8033,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458370</v>
+        <v>128458672</v>
       </c>
       <c r="B72" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8044,21 +8044,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679433</v>
+        <v>679298</v>
       </c>
       <c r="R72" t="n">
-        <v>7117926</v>
+        <v>7118058</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458664</v>
+        <v>128458681</v>
       </c>
       <c r="B73" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8141,21 +8141,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679459</v>
+        <v>679506</v>
       </c>
       <c r="R73" t="n">
-        <v>7118087</v>
+        <v>7118062</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8227,32 +8227,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458642</v>
+        <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>80254</v>
+        <v>79124</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679445</v>
+        <v>679436</v>
       </c>
       <c r="R74" t="n">
-        <v>7118102</v>
+        <v>7118086</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,10 +8324,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458671</v>
+        <v>128458389</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679436</v>
+        <v>679512</v>
       </c>
       <c r="R75" t="n">
-        <v>7118086</v>
+        <v>7118001</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458389</v>
+        <v>128458642</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>80258</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679512</v>
+        <v>679445</v>
       </c>
       <c r="R76" t="n">
-        <v>7118001</v>
+        <v>7118102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458349</v>
+        <v>128458675</v>
       </c>
       <c r="B77" t="n">
-        <v>80254</v>
+        <v>79124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679455</v>
+        <v>679390</v>
       </c>
       <c r="R77" t="n">
-        <v>7117858</v>
+        <v>7118002</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,10 +8615,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458641</v>
+        <v>128458349</v>
       </c>
       <c r="B78" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679393</v>
+        <v>679455</v>
       </c>
       <c r="R78" t="n">
-        <v>7118025</v>
+        <v>7117858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458675</v>
+        <v>128458641</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>80258</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679390</v>
+        <v>679393</v>
       </c>
       <c r="R79" t="n">
-        <v>7118002</v>
+        <v>7118025</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128458645</v>
+        <v>128458638</v>
       </c>
       <c r="B80" t="n">
-        <v>57713</v>
+        <v>79156</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8820,21 +8820,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>679307</v>
+        <v>679347</v>
       </c>
       <c r="R80" t="n">
-        <v>7117932</v>
+        <v>7117856</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,6 +8888,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8906,27 +8907,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128458377</v>
+        <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>58086</v>
+        <v>57717</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8941,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>679279</v>
+        <v>679307</v>
       </c>
       <c r="R81" t="n">
-        <v>7118000</v>
+        <v>7117932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9003,32 +9004,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128458638</v>
+        <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>79152</v>
+        <v>58090</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9038,10 +9039,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>679347</v>
+        <v>679279</v>
       </c>
       <c r="R82" t="n">
-        <v>7117856</v>
+        <v>7118000</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9082,7 +9083,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458658</v>
+        <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679386</v>
+        <v>679315</v>
       </c>
       <c r="R23" t="n">
-        <v>7118036</v>
+        <v>7118058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,11 +3282,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3313,7 +3308,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458657</v>
+        <v>128458658</v>
       </c>
       <c r="B24" t="n">
         <v>80229</v>
@@ -3348,10 +3343,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679407</v>
+        <v>679386</v>
       </c>
       <c r="R24" t="n">
-        <v>7117906</v>
+        <v>7118036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3388,7 +3383,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>björk</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458385</v>
+        <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3426,21 +3421,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3445,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679315</v>
+        <v>679407</v>
       </c>
       <c r="R25" t="n">
-        <v>7118058</v>
+        <v>7117906</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3486,6 +3481,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3614,10 +3614,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458381</v>
+        <v>128458356</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679414</v>
+        <v>679480</v>
       </c>
       <c r="R27" t="n">
-        <v>7117929</v>
+        <v>7117930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,7 +3698,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3717,7 +3716,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458673</v>
+        <v>128458381</v>
       </c>
       <c r="B28" t="n">
         <v>79124</v>
@@ -3752,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679328</v>
+        <v>679414</v>
       </c>
       <c r="R28" t="n">
-        <v>7117932</v>
+        <v>7117929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,12 +3789,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3814,10 +3819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458356</v>
+        <v>128458673</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3825,21 +3830,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,10 +3854,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679480</v>
+        <v>679328</v>
       </c>
       <c r="R29" t="n">
-        <v>7117930</v>
+        <v>7117932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3885,11 +3890,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458692</v>
+        <v>128458342</v>
       </c>
       <c r="B48" t="n">
-        <v>88908</v>
+        <v>56910</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679349</v>
+        <v>679446</v>
       </c>
       <c r="R48" t="n">
-        <v>7117913</v>
+        <v>7117918</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458388</v>
+        <v>128458692</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>88908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679456</v>
+        <v>679349</v>
       </c>
       <c r="R49" t="n">
-        <v>7118056</v>
+        <v>7117913</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458662</v>
+        <v>128458388</v>
       </c>
       <c r="B50" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679403</v>
+        <v>679456</v>
       </c>
       <c r="R50" t="n">
-        <v>7117960</v>
+        <v>7118056</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458373</v>
+        <v>128458662</v>
       </c>
       <c r="B51" t="n">
         <v>80229</v>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679404</v>
+        <v>679403</v>
       </c>
       <c r="R51" t="n">
-        <v>7117977</v>
+        <v>7117960</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458374</v>
+        <v>128458373</v>
       </c>
       <c r="B52" t="n">
         <v>80229</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679493</v>
+        <v>679404</v>
       </c>
       <c r="R52" t="n">
-        <v>7118012</v>
+        <v>7117977</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,32 +6155,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458342</v>
+        <v>128458374</v>
       </c>
       <c r="B53" t="n">
-        <v>56910</v>
+        <v>80229</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679446</v>
+        <v>679493</v>
       </c>
       <c r="R53" t="n">
-        <v>7117918</v>
+        <v>7118012</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458678</v>
+        <v>128458378</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>58090</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679369</v>
+        <v>679383</v>
       </c>
       <c r="R59" t="n">
-        <v>7118112</v>
+        <v>7117814</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458387</v>
+        <v>128458678</v>
       </c>
       <c r="B60" t="n">
         <v>79124</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679461</v>
+        <v>679369</v>
       </c>
       <c r="R60" t="n">
-        <v>7117988</v>
+        <v>7118112</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458378</v>
+        <v>128458387</v>
       </c>
       <c r="B61" t="n">
-        <v>58090</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679383</v>
+        <v>679461</v>
       </c>
       <c r="R61" t="n">
-        <v>7117814</v>
+        <v>7117988</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128458680</v>
+        <v>128458353</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679472</v>
+        <v>679512</v>
       </c>
       <c r="R63" t="n">
-        <v>7118058</v>
+        <v>7118001</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7220,6 +7220,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7246,10 +7251,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128458366</v>
+        <v>128458680</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7257,21 +7262,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679455</v>
+        <v>679472</v>
       </c>
       <c r="R64" t="n">
-        <v>7117858</v>
+        <v>7118058</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7343,7 +7348,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128458663</v>
+        <v>128458366</v>
       </c>
       <c r="B65" t="n">
         <v>80229</v>
@@ -7378,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679446</v>
+        <v>679455</v>
       </c>
       <c r="R65" t="n">
-        <v>7118101</v>
+        <v>7117858</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,32 +7445,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128458375</v>
+        <v>128458663</v>
       </c>
       <c r="B66" t="n">
-        <v>80265</v>
+        <v>80229</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679437</v>
+        <v>679446</v>
       </c>
       <c r="R66" t="n">
-        <v>7117961</v>
+        <v>7118101</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7537,32 +7542,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128458353</v>
+        <v>128458375</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>80265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7572,10 +7577,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>679512</v>
+        <v>679437</v>
       </c>
       <c r="R67" t="n">
-        <v>7118001</v>
+        <v>7117961</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7608,11 +7613,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8227,32 +8227,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458671</v>
+        <v>128458642</v>
       </c>
       <c r="B74" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679436</v>
+        <v>679445</v>
       </c>
       <c r="R74" t="n">
-        <v>7118086</v>
+        <v>7118102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,7 +8324,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458389</v>
+        <v>128458671</v>
       </c>
       <c r="B75" t="n">
         <v>79124</v>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679512</v>
+        <v>679436</v>
       </c>
       <c r="R75" t="n">
-        <v>7118001</v>
+        <v>7118086</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8421,32 +8421,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128458642</v>
+        <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>679445</v>
+        <v>679512</v>
       </c>
       <c r="R76" t="n">
-        <v>7118102</v>
+        <v>7118001</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458675</v>
+        <v>128458349</v>
       </c>
       <c r="B77" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679390</v>
+        <v>679455</v>
       </c>
       <c r="R77" t="n">
-        <v>7118002</v>
+        <v>7117858</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,7 +8615,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458349</v>
+        <v>128458641</v>
       </c>
       <c r="B78" t="n">
         <v>80258</v>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679455</v>
+        <v>679393</v>
       </c>
       <c r="R78" t="n">
-        <v>7117858</v>
+        <v>7118025</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458641</v>
+        <v>128458675</v>
       </c>
       <c r="B79" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679393</v>
+        <v>679390</v>
       </c>
       <c r="R79" t="n">
-        <v>7118025</v>
+        <v>7118002</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9390,6 +9390,218 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129001134</v>
+      </c>
+      <c r="B86" t="n">
+        <v>82983</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>679310</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7117992</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129001142</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>679316</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7118085</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>128458385</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128458658</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>128458657</v>
       </c>
       <c r="B25" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>128458648</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>128458356</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>128458381</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>128458673</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>128458365</v>
       </c>
       <c r="B30" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>128458344</v>
       </c>
       <c r="B31" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128458670</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>128458399</v>
       </c>
       <c r="B33" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,32 +4305,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458372</v>
+        <v>128458644</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>91524</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679409</v>
+        <v>679456</v>
       </c>
       <c r="R34" t="n">
-        <v>7117952</v>
+        <v>7118095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458369</v>
+        <v>128458679</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679437</v>
+        <v>679434</v>
       </c>
       <c r="R35" t="n">
-        <v>7117961</v>
+        <v>7118112</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458659</v>
+        <v>128458372</v>
       </c>
       <c r="B36" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679419</v>
+        <v>679409</v>
       </c>
       <c r="R36" t="n">
-        <v>7118102</v>
+        <v>7117952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,32 +4596,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458644</v>
+        <v>128458386</v>
       </c>
       <c r="B37" t="n">
-        <v>91519</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679456</v>
+        <v>679411</v>
       </c>
       <c r="R37" t="n">
-        <v>7118095</v>
+        <v>7117970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458679</v>
+        <v>128458369</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4704,21 +4704,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679434</v>
+        <v>679437</v>
       </c>
       <c r="R38" t="n">
-        <v>7118112</v>
+        <v>7117961</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458386</v>
+        <v>128458659</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679411</v>
+        <v>679419</v>
       </c>
       <c r="R39" t="n">
-        <v>7117970</v>
+        <v>7118102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458677</v>
+        <v>128458640</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679355</v>
+        <v>679458</v>
       </c>
       <c r="R40" t="n">
-        <v>7118031</v>
+        <v>7118097</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4984,32 +4984,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458640</v>
+        <v>128458364</v>
       </c>
       <c r="B41" t="n">
-        <v>80258</v>
+        <v>80134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679458</v>
+        <v>679421</v>
       </c>
       <c r="R41" t="n">
-        <v>7118097</v>
+        <v>7117929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5063,6 +5063,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5081,10 +5082,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458364</v>
+        <v>128458677</v>
       </c>
       <c r="B42" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,21 +5093,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5116,10 +5117,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679421</v>
+        <v>679355</v>
       </c>
       <c r="R42" t="n">
-        <v>7117929</v>
+        <v>7118031</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5160,7 +5161,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>128458660</v>
       </c>
       <c r="B43" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128458340</v>
       </c>
       <c r="B44" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128458384</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>128458661</v>
       </c>
       <c r="B46" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>128458371</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5670,32 +5670,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458342</v>
+        <v>128458662</v>
       </c>
       <c r="B48" t="n">
-        <v>56910</v>
+        <v>80134</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679446</v>
+        <v>679403</v>
       </c>
       <c r="R48" t="n">
-        <v>7117918</v>
+        <v>7117960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458692</v>
+        <v>128458373</v>
       </c>
       <c r="B49" t="n">
-        <v>88908</v>
+        <v>80134</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679349</v>
+        <v>679404</v>
       </c>
       <c r="R49" t="n">
-        <v>7117913</v>
+        <v>7117977</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128458388</v>
+        <v>128458374</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679456</v>
+        <v>679493</v>
       </c>
       <c r="R50" t="n">
-        <v>7118056</v>
+        <v>7118012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128458662</v>
+        <v>128458388</v>
       </c>
       <c r="B51" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679403</v>
+        <v>679456</v>
       </c>
       <c r="R51" t="n">
-        <v>7117960</v>
+        <v>7118056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,32 +6058,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128458373</v>
+        <v>128458342</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>56913</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679404</v>
+        <v>679446</v>
       </c>
       <c r="R52" t="n">
-        <v>7117977</v>
+        <v>7117918</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,10 +6155,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128458374</v>
+        <v>128458692</v>
       </c>
       <c r="B53" t="n">
-        <v>80229</v>
+        <v>88913</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,21 +6166,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679493</v>
+        <v>679349</v>
       </c>
       <c r="R53" t="n">
-        <v>7118012</v>
+        <v>7117913</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128458351</v>
+        <v>128458643</v>
       </c>
       <c r="B54" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679464</v>
+        <v>679460</v>
       </c>
       <c r="R54" t="n">
-        <v>7117976</v>
+        <v>7118089</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,32 +6349,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128458643</v>
+        <v>128458368</v>
       </c>
       <c r="B55" t="n">
-        <v>80258</v>
+        <v>80134</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679460</v>
+        <v>679446</v>
       </c>
       <c r="R55" t="n">
-        <v>7118089</v>
+        <v>7117937</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,32 +6446,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128458368</v>
+        <v>128458351</v>
       </c>
       <c r="B56" t="n">
-        <v>80229</v>
+        <v>80163</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679446</v>
+        <v>679464</v>
       </c>
       <c r="R56" t="n">
-        <v>7117937</v>
+        <v>7117976</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6546,7 +6546,7 @@
         <v>128458358</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128458350</v>
       </c>
       <c r="B58" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128458378</v>
+        <v>128458678</v>
       </c>
       <c r="B59" t="n">
-        <v>58090</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679383</v>
+        <v>679369</v>
       </c>
       <c r="R59" t="n">
-        <v>7117814</v>
+        <v>7118112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128458678</v>
+        <v>128458387</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679369</v>
+        <v>679461</v>
       </c>
       <c r="R60" t="n">
-        <v>7118112</v>
+        <v>7117988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6936,32 +6936,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128458387</v>
+        <v>128458378</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>58093</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679461</v>
+        <v>679383</v>
       </c>
       <c r="R61" t="n">
-        <v>7117988</v>
+        <v>7117814</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
         <v>128458367</v>
       </c>
       <c r="B62" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>128458353</v>
       </c>
       <c r="B63" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>128458680</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>128458366</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>128458663</v>
       </c>
       <c r="B66" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>128458375</v>
       </c>
       <c r="B67" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,10 +7639,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128458370</v>
+        <v>128458674</v>
       </c>
       <c r="B68" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7650,21 +7650,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>679433</v>
+        <v>679408</v>
       </c>
       <c r="R68" t="n">
-        <v>7117926</v>
+        <v>7117925</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128458664</v>
+        <v>128458672</v>
       </c>
       <c r="B69" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7747,21 +7747,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>679459</v>
+        <v>679298</v>
       </c>
       <c r="R69" t="n">
-        <v>7118087</v>
+        <v>7118058</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7833,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128458674</v>
+        <v>128458370</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7844,21 +7844,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>679408</v>
+        <v>679433</v>
       </c>
       <c r="R70" t="n">
-        <v>7117925</v>
+        <v>7117926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128458382</v>
+        <v>128458681</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>679440</v>
+        <v>679506</v>
       </c>
       <c r="R71" t="n">
-        <v>7117885</v>
+        <v>7118062</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8003,18 +8003,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8033,10 +8027,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128458672</v>
+        <v>128458664</v>
       </c>
       <c r="B72" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8044,21 +8038,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8068,10 +8062,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>679298</v>
+        <v>679459</v>
       </c>
       <c r="R72" t="n">
-        <v>7118058</v>
+        <v>7118087</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8130,10 +8124,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128458681</v>
+        <v>128458382</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8165,10 +8159,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>679506</v>
+        <v>679440</v>
       </c>
       <c r="R73" t="n">
-        <v>7118062</v>
+        <v>7117885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8203,12 +8197,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8227,32 +8227,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128458642</v>
+        <v>128458671</v>
       </c>
       <c r="B74" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>679445</v>
+        <v>679436</v>
       </c>
       <c r="R74" t="n">
-        <v>7118102</v>
+        <v>7118086</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8324,32 +8324,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128458671</v>
+        <v>128458642</v>
       </c>
       <c r="B75" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>679436</v>
+        <v>679445</v>
       </c>
       <c r="R75" t="n">
-        <v>7118086</v>
+        <v>7118102</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8424,7 +8424,7 @@
         <v>128458389</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8518,32 +8518,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128458349</v>
+        <v>128458675</v>
       </c>
       <c r="B77" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>679455</v>
+        <v>679390</v>
       </c>
       <c r="R77" t="n">
-        <v>7117858</v>
+        <v>7118002</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8615,10 +8615,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128458641</v>
+        <v>128458349</v>
       </c>
       <c r="B78" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>679393</v>
+        <v>679455</v>
       </c>
       <c r="R78" t="n">
-        <v>7118025</v>
+        <v>7117858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128458675</v>
+        <v>128458641</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>679390</v>
+        <v>679393</v>
       </c>
       <c r="R79" t="n">
-        <v>7118002</v>
+        <v>7118025</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8812,7 +8812,7 @@
         <v>128458638</v>
       </c>
       <c r="B80" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128458645</v>
       </c>
       <c r="B81" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128458377</v>
       </c>
       <c r="B82" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>128472161</v>
       </c>
       <c r="B83" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>128472175</v>
       </c>
       <c r="B84" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>128472160</v>
       </c>
       <c r="B85" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9602,6 +9602,112 @@
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129224238</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>679424</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7117873</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9518,14 +9518,10 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>1</t>
@@ -9607,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9624,14 +9620,10 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>1</t>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9395,7 +9395,7 @@
         <v>129001134</v>
       </c>
       <c r="B86" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9501,7 +9501,7 @@
         <v>129001142</v>
       </c>
       <c r="B87" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -9603,7 +9603,7 @@
         <v>129224238</v>
       </c>
       <c r="B88" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>126864915</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126859342</v>
       </c>
       <c r="B22" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30689-2025 artfynd.xlsx
+++ b/artfynd/A 30689-2025 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>126864915</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126859342</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
